--- a/research/traditional_assets/database/data/bahrain/bahrain_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_food_wholesalers.xlsx
@@ -1133,43 +1133,43 @@
         <v>4.11764705882353</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>180.38697638729</v>
       </c>
       <c r="G2">
         <v>3.82278481012658</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.115443037974684</v>
       </c>
       <c r="I2">
         <v>0.331140350877193</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>61</v>
       </c>
       <c r="L2">
-        <v>119.208858326147</v>
+        <v>118.212582563626</v>
       </c>
       <c r="M2">
         <v>82.36</v>
       </c>
       <c r="N2">
-        <v>110.368858326147</v>
+        <v>110.284582563626</v>
       </c>
       <c r="O2">
         <v>30.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="Q2">
         <v>0.124714142004028</v>
       </c>
       <c r="R2">
-        <v>0.104687704684284</v>
+        <v>0.104732704684284</v>
       </c>
       <c r="S2">
         <v>0.106277188197372</v>
@@ -1191,13 +1191,13 @@
         <v>0.133841945364044</v>
       </c>
       <c r="X2">
-        <v>0.104687704684284</v>
+        <v>0.105282529984125</v>
       </c>
       <c r="Y2">
         <v>0.754148262878191</v>
       </c>
       <c r="Z2">
-        <v>0.504419342495281</v>
+        <v>0.509514487368971</v>
       </c>
       <c r="AA2">
         <v>30.2</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1046877046842839</v>
+        <v>0.1047327046842839</v>
       </c>
       <c r="C2">
-        <v>119.208858326147</v>
+        <v>118.2125825636263</v>
       </c>
       <c r="D2">
-        <v>110.368858326147</v>
+        <v>110.2845825636263</v>
       </c>
       <c r="E2">
-        <v>-30.2</v>
+        <v>-29.288</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="G2">
         <v>8.84</v>
@@ -1451,28 +1451,28 @@
         <v>8.275</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0458736</v>
       </c>
       <c r="N2">
-        <v>8.275</v>
+        <v>8.2291264</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>8.275</v>
+        <v>8.2291264</v>
       </c>
       <c r="Q2">
-        <v>9.875</v>
+        <v>9.8291264</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1046877046842839</v>
+        <v>0.1052825299841251</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5095144873689709</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>180.3869763872903</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1047327046842839</v>
+        <v>0.1047777046842839</v>
       </c>
       <c r="C3">
-        <v>118.2125825636263</v>
+        <v>117.2164354059515</v>
       </c>
       <c r="D3">
-        <v>110.2845825636263</v>
+        <v>110.2004354059515</v>
       </c>
       <c r="E3">
-        <v>-29.288</v>
+        <v>-28.376</v>
       </c>
       <c r="F3">
-        <v>0.912</v>
+        <v>1.824</v>
       </c>
       <c r="G3">
         <v>8.84</v>
@@ -1533,28 +1533,28 @@
         <v>8.275</v>
       </c>
       <c r="M3">
-        <v>0.0458736</v>
+        <v>0.0917472</v>
       </c>
       <c r="N3">
-        <v>8.2291264</v>
+        <v>8.1832528</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>8.2291264</v>
+        <v>8.1832528</v>
       </c>
       <c r="Q3">
-        <v>9.8291264</v>
+        <v>9.7832528</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1052825299841251</v>
+        <v>0.1058894945757999</v>
       </c>
       <c r="T3">
-        <v>0.5095144873689709</v>
+        <v>0.5147136147911031</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>180.3869763872903</v>
+        <v>90.19348819364515</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1047777046842839</v>
+        <v>0.1048227046842839</v>
       </c>
       <c r="C4">
-        <v>117.2164354059515</v>
+        <v>116.2204165589707</v>
       </c>
       <c r="D4">
-        <v>110.2004354059515</v>
+        <v>110.1164165589707</v>
       </c>
       <c r="E4">
-        <v>-28.376</v>
+        <v>-27.464</v>
       </c>
       <c r="F4">
-        <v>1.824</v>
+        <v>2.736</v>
       </c>
       <c r="G4">
         <v>8.84</v>
@@ -1615,28 +1615,28 @@
         <v>8.275</v>
       </c>
       <c r="M4">
-        <v>0.0917472</v>
+        <v>0.1376208</v>
       </c>
       <c r="N4">
-        <v>8.1832528</v>
+        <v>8.1373792</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>8.1832528</v>
+        <v>8.1373792</v>
       </c>
       <c r="Q4">
-        <v>9.7832528</v>
+        <v>9.737379199999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1058894945757999</v>
+        <v>0.1065089739013236</v>
       </c>
       <c r="T4">
-        <v>0.5147136147911031</v>
+        <v>0.5200199407167846</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.19348819364515</v>
+        <v>60.12899212909677</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1048227046842839</v>
+        <v>0.1048677046842839</v>
       </c>
       <c r="C5">
-        <v>116.2204165589707</v>
+        <v>115.2245257294279</v>
       </c>
       <c r="D5">
-        <v>110.1164165589707</v>
+        <v>110.0325257294278</v>
       </c>
       <c r="E5">
-        <v>-27.464</v>
+        <v>-26.552</v>
       </c>
       <c r="F5">
-        <v>2.736</v>
+        <v>3.648</v>
       </c>
       <c r="G5">
         <v>8.84</v>
@@ -1697,28 +1697,28 @@
         <v>8.275</v>
       </c>
       <c r="M5">
-        <v>0.1376208</v>
+        <v>0.1834944</v>
       </c>
       <c r="N5">
-        <v>8.1373792</v>
+        <v>8.0915056</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>8.1373792</v>
+        <v>8.0915056</v>
       </c>
       <c r="Q5">
-        <v>9.737379199999999</v>
+        <v>9.691505599999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1065089739013236</v>
+        <v>0.107141359046129</v>
       </c>
       <c r="T5">
-        <v>0.5200199407167846</v>
+        <v>0.5254368150992512</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.12899212909677</v>
+        <v>45.09674409682257</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1048677046842839</v>
+        <v>0.1049127046842839</v>
       </c>
       <c r="C6">
-        <v>115.2245257294279</v>
+        <v>114.2287626249604</v>
       </c>
       <c r="D6">
-        <v>110.0325257294278</v>
+        <v>109.9487626249604</v>
       </c>
       <c r="E6">
-        <v>-26.552</v>
+        <v>-25.64</v>
       </c>
       <c r="F6">
-        <v>3.648</v>
+        <v>4.56</v>
       </c>
       <c r="G6">
         <v>8.84</v>
@@ -1779,28 +1779,28 @@
         <v>8.275</v>
       </c>
       <c r="M6">
-        <v>0.1834944</v>
+        <v>0.229368</v>
       </c>
       <c r="N6">
-        <v>8.0915056</v>
+        <v>8.045632000000001</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>8.0915056</v>
+        <v>8.045632000000001</v>
       </c>
       <c r="Q6">
-        <v>9.691505599999999</v>
+        <v>9.645632000000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.107141359046129</v>
+        <v>0.1077870575624041</v>
       </c>
       <c r="T6">
-        <v>0.5254368150992512</v>
+        <v>0.5309677289424011</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.09674409682257</v>
+        <v>36.07739527745806</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1049127046842839</v>
+        <v>0.1049577046842839</v>
       </c>
       <c r="C7">
-        <v>114.2287626249604</v>
+        <v>113.233126954095</v>
       </c>
       <c r="D7">
-        <v>109.9487626249604</v>
+        <v>109.865126954095</v>
       </c>
       <c r="E7">
-        <v>-25.64</v>
+        <v>-24.728</v>
       </c>
       <c r="F7">
-        <v>4.56</v>
+        <v>5.472</v>
       </c>
       <c r="G7">
         <v>8.84</v>
@@ -1861,28 +1861,28 @@
         <v>8.275</v>
       </c>
       <c r="M7">
-        <v>0.229368</v>
+        <v>0.2752416</v>
       </c>
       <c r="N7">
-        <v>8.045632000000001</v>
+        <v>7.9997584</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>8.045632000000001</v>
+        <v>7.9997584</v>
       </c>
       <c r="Q7">
-        <v>9.645632000000001</v>
+        <v>9.599758400000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1077870575624041</v>
+        <v>0.1084464943449829</v>
       </c>
       <c r="T7">
-        <v>0.5309677289424011</v>
+        <v>0.5366163218034905</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.07739527745806</v>
+        <v>30.06449606454838</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1049577046842839</v>
+        <v>0.1050027046842839</v>
       </c>
       <c r="C8">
-        <v>113.2331269540951</v>
+        <v>112.2376184262449</v>
       </c>
       <c r="D8">
-        <v>109.8651269540951</v>
+        <v>109.7816184262448</v>
       </c>
       <c r="E8">
-        <v>-24.728</v>
+        <v>-23.816</v>
       </c>
       <c r="F8">
-        <v>5.472</v>
+        <v>6.383999999999999</v>
       </c>
       <c r="G8">
         <v>8.84</v>
@@ -1943,28 +1943,28 @@
         <v>8.275</v>
       </c>
       <c r="M8">
-        <v>0.2752416</v>
+        <v>0.3211151999999999</v>
       </c>
       <c r="N8">
-        <v>7.9997584</v>
+        <v>7.953884800000001</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>7.9997584</v>
+        <v>7.953884800000001</v>
       </c>
       <c r="Q8">
-        <v>9.599758400000001</v>
+        <v>9.553884800000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1084464943449829</v>
+        <v>0.1091201125637461</v>
       </c>
       <c r="T8">
-        <v>0.5366163218034905</v>
+        <v>0.5423863897798721</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.06449606454839</v>
+        <v>25.76956805532719</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1050027046842839</v>
+        <v>0.1050477046842839</v>
       </c>
       <c r="C9">
-        <v>112.2376184262449</v>
+        <v>111.2422367517056</v>
       </c>
       <c r="D9">
-        <v>109.7816184262449</v>
+        <v>109.6982367517056</v>
       </c>
       <c r="E9">
-        <v>-23.816</v>
+        <v>-22.904</v>
       </c>
       <c r="F9">
-        <v>6.384000000000001</v>
+        <v>7.296</v>
       </c>
       <c r="G9">
         <v>8.84</v>
@@ -2025,28 +2025,28 @@
         <v>8.275</v>
       </c>
       <c r="M9">
-        <v>0.3211152</v>
+        <v>0.3669888</v>
       </c>
       <c r="N9">
-        <v>7.9538848</v>
+        <v>7.908011200000001</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>7.9538848</v>
+        <v>7.908011200000001</v>
       </c>
       <c r="Q9">
-        <v>9.553884800000001</v>
+        <v>9.5080112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1091201125637461</v>
+        <v>0.1098083746568303</v>
       </c>
       <c r="T9">
-        <v>0.5423863897798721</v>
+        <v>0.5482818940166099</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.76956805532718</v>
+        <v>22.54837204841129</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1050477046842839</v>
+        <v>0.1050927046842839</v>
       </c>
       <c r="C10">
-        <v>111.2422367517056</v>
+        <v>110.2469816416527</v>
       </c>
       <c r="D10">
-        <v>109.6982367517056</v>
+        <v>109.6149816416526</v>
       </c>
       <c r="E10">
-        <v>-22.904</v>
+        <v>-21.992</v>
       </c>
       <c r="F10">
-        <v>7.296</v>
+        <v>8.208</v>
       </c>
       <c r="G10">
         <v>8.84</v>
@@ -2107,28 +2107,28 @@
         <v>8.275</v>
       </c>
       <c r="M10">
-        <v>0.3669888</v>
+        <v>0.4128624</v>
       </c>
       <c r="N10">
-        <v>7.908011200000001</v>
+        <v>7.862137600000001</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>7.908011200000001</v>
+        <v>7.862137600000001</v>
       </c>
       <c r="Q10">
-        <v>9.5080112</v>
+        <v>9.4621376</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1098083746568303</v>
+        <v>0.1105117633893229</v>
       </c>
       <c r="T10">
-        <v>0.5482818940166099</v>
+        <v>0.5543069697750342</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.54837204841129</v>
+        <v>20.04299737636559</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1050927046842839</v>
+        <v>0.1051377046842839</v>
       </c>
       <c r="C11">
-        <v>110.2469816416527</v>
+        <v>109.2518528081375</v>
       </c>
       <c r="D11">
-        <v>109.6149816416526</v>
+        <v>109.5318528081375</v>
       </c>
       <c r="E11">
-        <v>-21.992</v>
+        <v>-21.08</v>
       </c>
       <c r="F11">
-        <v>8.208</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G11">
         <v>8.84</v>
@@ -2189,28 +2189,28 @@
         <v>8.275</v>
       </c>
       <c r="M11">
-        <v>0.4128624</v>
+        <v>0.4587359999999999</v>
       </c>
       <c r="N11">
-        <v>7.862137600000001</v>
+        <v>7.816264</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>7.862137600000001</v>
+        <v>7.816264</v>
       </c>
       <c r="Q11">
-        <v>9.4621376</v>
+        <v>9.416264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1105117633893229</v>
+        <v>0.1112307829825376</v>
       </c>
       <c r="T11">
-        <v>0.5543069697750342</v>
+        <v>0.5604659361058679</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.04299737636559</v>
+        <v>18.03869763872903</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1051377046842839</v>
+        <v>0.1051827046842839</v>
       </c>
       <c r="C12">
-        <v>109.2518528081375</v>
+        <v>108.2568499640843</v>
       </c>
       <c r="D12">
-        <v>109.5318528081375</v>
+        <v>109.4488499640843</v>
       </c>
       <c r="E12">
-        <v>-21.08</v>
+        <v>-20.168</v>
       </c>
       <c r="F12">
-        <v>9.120000000000001</v>
+        <v>10.032</v>
       </c>
       <c r="G12">
         <v>8.84</v>
@@ -2271,28 +2271,28 @@
         <v>8.275</v>
       </c>
       <c r="M12">
-        <v>0.458736</v>
+        <v>0.5046096</v>
       </c>
       <c r="N12">
-        <v>7.816264</v>
+        <v>7.7703904</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>7.816264</v>
+        <v>7.7703904</v>
       </c>
       <c r="Q12">
-        <v>9.416264</v>
+        <v>9.3703904</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1112307829825376</v>
+        <v>0.1119659603194201</v>
       </c>
       <c r="T12">
-        <v>0.5604659361058679</v>
+        <v>0.5667633061744731</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.03869763872903</v>
+        <v>16.39881603520821</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1051827046842839</v>
+        <v>0.1052277046842839</v>
       </c>
       <c r="C13">
-        <v>108.2568499640843</v>
+        <v>107.2619728232869</v>
       </c>
       <c r="D13">
-        <v>109.4488499640843</v>
+        <v>109.3659728232869</v>
       </c>
       <c r="E13">
-        <v>-20.168</v>
+        <v>-19.256</v>
       </c>
       <c r="F13">
-        <v>10.032</v>
+        <v>10.944</v>
       </c>
       <c r="G13">
         <v>8.84</v>
@@ -2353,28 +2353,28 @@
         <v>8.275</v>
       </c>
       <c r="M13">
-        <v>0.5046096</v>
+        <v>0.5504832</v>
       </c>
       <c r="N13">
-        <v>7.7703904</v>
+        <v>7.7245168</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>7.7703904</v>
+        <v>7.7245168</v>
       </c>
       <c r="Q13">
-        <v>9.3703904</v>
+        <v>9.3245168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1119659603194201</v>
+        <v>0.1127178462321408</v>
       </c>
       <c r="T13">
-        <v>0.5667633061744731</v>
+        <v>0.573203798290092</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.39881603520821</v>
+        <v>15.03224803227419</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1052277046842839</v>
+        <v>0.1052727046842839</v>
       </c>
       <c r="C14">
-        <v>107.2619728232869</v>
+        <v>106.2672211004054</v>
       </c>
       <c r="D14">
-        <v>109.3659728232869</v>
+        <v>109.2832211004054</v>
       </c>
       <c r="E14">
-        <v>-19.256</v>
+        <v>-18.344</v>
       </c>
       <c r="F14">
-        <v>10.944</v>
+        <v>11.856</v>
       </c>
       <c r="G14">
         <v>8.84</v>
@@ -2435,28 +2435,28 @@
         <v>8.275</v>
       </c>
       <c r="M14">
-        <v>0.5504832</v>
+        <v>0.5963568</v>
       </c>
       <c r="N14">
-        <v>7.7245168</v>
+        <v>7.678643200000001</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>7.7245168</v>
+        <v>7.678643200000001</v>
       </c>
       <c r="Q14">
-        <v>9.3245168</v>
+        <v>9.278643200000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1127178462321408</v>
+        <v>0.1134870168784872</v>
       </c>
       <c r="T14">
-        <v>0.573203798290092</v>
+        <v>0.5797923476957253</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.03224803227419</v>
+        <v>13.87592126056079</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1052727046842839</v>
+        <v>0.1053177046842839</v>
       </c>
       <c r="C15">
-        <v>106.2672211004054</v>
+        <v>105.2725945109627</v>
       </c>
       <c r="D15">
-        <v>109.2832211004054</v>
+        <v>109.2005945109627</v>
       </c>
       <c r="E15">
-        <v>-18.344</v>
+        <v>-17.432</v>
       </c>
       <c r="F15">
-        <v>11.856</v>
+        <v>12.768</v>
       </c>
       <c r="G15">
         <v>8.84</v>
@@ -2517,28 +2517,28 @@
         <v>8.275</v>
       </c>
       <c r="M15">
-        <v>0.5963568</v>
+        <v>0.6422304000000001</v>
       </c>
       <c r="N15">
-        <v>7.678643200000001</v>
+        <v>7.6327696</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>7.678643200000001</v>
+        <v>7.6327696</v>
       </c>
       <c r="Q15">
-        <v>9.278643200000001</v>
+        <v>9.232769600000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1134870168784872</v>
+        <v>0.1142740752142836</v>
       </c>
       <c r="T15">
-        <v>0.5797923476957253</v>
+        <v>0.5865341191805594</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.87592126056079</v>
+        <v>12.88478402766359</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1053177046842839</v>
+        <v>0.1055877046842839</v>
       </c>
       <c r="C16">
-        <v>105.2725945109627</v>
+        <v>103.8674469537241</v>
       </c>
       <c r="D16">
-        <v>109.2005945109627</v>
+        <v>108.7074469537241</v>
       </c>
       <c r="E16">
-        <v>-17.432</v>
+        <v>-16.52</v>
       </c>
       <c r="F16">
-        <v>12.768</v>
+        <v>13.68</v>
       </c>
       <c r="G16">
         <v>8.84</v>
@@ -2599,45 +2599,45 @@
         <v>8.275</v>
       </c>
       <c r="M16">
-        <v>0.6422304000000001</v>
+        <v>0.7086240000000001</v>
       </c>
       <c r="N16">
-        <v>7.6327696</v>
+        <v>7.566376</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>7.6327696</v>
+        <v>7.566376</v>
       </c>
       <c r="Q16">
-        <v>9.232769600000001</v>
+        <v>9.166376</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1142740752142836</v>
+        <v>0.1150796525697457</v>
       </c>
       <c r="T16">
-        <v>0.5865341191805594</v>
+        <v>0.5934345205826836</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.88478402766359</v>
+        <v>11.67756101966628</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1055877046842839</v>
+        <v>0.1056477046842839</v>
       </c>
       <c r="C17">
-        <v>103.8674469537241</v>
+        <v>102.8464628773651</v>
       </c>
       <c r="D17">
-        <v>108.7074469537241</v>
+        <v>108.5984628773651</v>
       </c>
       <c r="E17">
-        <v>-16.52</v>
+        <v>-15.608</v>
       </c>
       <c r="F17">
-        <v>13.68</v>
+        <v>14.592</v>
       </c>
       <c r="G17">
         <v>8.84</v>
@@ -2681,28 +2681,28 @@
         <v>8.275</v>
       </c>
       <c r="M17">
-        <v>0.7086239999999999</v>
+        <v>0.7558656</v>
       </c>
       <c r="N17">
-        <v>7.566376</v>
+        <v>7.5191344</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>7.566376</v>
+        <v>7.5191344</v>
       </c>
       <c r="Q17">
-        <v>9.166376</v>
+        <v>9.1191344</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1150796525697457</v>
+        <v>0.1159044103384332</v>
       </c>
       <c r="T17">
-        <v>0.5934345205826836</v>
+        <v>0.600499217256287</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.67756101966628</v>
+        <v>10.94771345593714</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1056477046842839</v>
+        <v>0.1057077046842839</v>
       </c>
       <c r="C18">
-        <v>102.8464628773651</v>
+        <v>101.8256971049661</v>
       </c>
       <c r="D18">
-        <v>108.5984628773651</v>
+        <v>108.4896971049661</v>
       </c>
       <c r="E18">
-        <v>-15.608</v>
+        <v>-14.696</v>
       </c>
       <c r="F18">
-        <v>14.592</v>
+        <v>15.504</v>
       </c>
       <c r="G18">
         <v>8.84</v>
@@ -2763,28 +2763,28 @@
         <v>8.275</v>
       </c>
       <c r="M18">
-        <v>0.7558656</v>
+        <v>0.8031072</v>
       </c>
       <c r="N18">
-        <v>7.5191344</v>
+        <v>7.4718928</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>7.5191344</v>
+        <v>7.4718928</v>
       </c>
       <c r="Q18">
-        <v>9.1191344</v>
+        <v>9.071892800000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1159044103384332</v>
+        <v>0.1167490417882938</v>
       </c>
       <c r="T18">
-        <v>0.600499217256287</v>
+        <v>0.607734147584676</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.94771345593714</v>
+        <v>10.30373031147025</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1057077046842839</v>
+        <v>0.1060737046842839</v>
       </c>
       <c r="C19">
-        <v>101.8256971049661</v>
+        <v>100.2549151477526</v>
       </c>
       <c r="D19">
-        <v>108.4896971049661</v>
+        <v>107.8309151477526</v>
       </c>
       <c r="E19">
-        <v>-14.696</v>
+        <v>-13.784</v>
       </c>
       <c r="F19">
-        <v>15.504</v>
+        <v>16.416</v>
       </c>
       <c r="G19">
         <v>8.84</v>
@@ -2845,45 +2845,45 @@
         <v>8.275</v>
       </c>
       <c r="M19">
-        <v>0.8031072</v>
+        <v>0.8782560000000001</v>
       </c>
       <c r="N19">
-        <v>7.4718928</v>
+        <v>7.396744</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>7.4718928</v>
+        <v>7.396744</v>
       </c>
       <c r="Q19">
-        <v>9.071892800000001</v>
+        <v>8.996744</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1167490417882938</v>
+        <v>0.1176142740052242</v>
       </c>
       <c r="T19">
-        <v>0.607734147584676</v>
+        <v>0.6151455396283916</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.30373031147025</v>
+        <v>9.422081944216719</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1060737046842839</v>
+        <v>0.1061507046842839</v>
       </c>
       <c r="C20">
-        <v>100.2549151477526</v>
+        <v>99.20533629909097</v>
       </c>
       <c r="D20">
-        <v>107.8309151477526</v>
+        <v>107.693336299091</v>
       </c>
       <c r="E20">
-        <v>-13.784</v>
+        <v>-12.872</v>
       </c>
       <c r="F20">
-        <v>16.416</v>
+        <v>17.328</v>
       </c>
       <c r="G20">
         <v>8.84</v>
@@ -2927,28 +2927,28 @@
         <v>8.275</v>
       </c>
       <c r="M20">
-        <v>0.878256</v>
+        <v>0.927048</v>
       </c>
       <c r="N20">
-        <v>7.396744</v>
+        <v>7.347952</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>7.396744</v>
+        <v>7.347952</v>
       </c>
       <c r="Q20">
-        <v>8.996744</v>
+        <v>8.947952000000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1176142740052242</v>
+        <v>0.1185008699805974</v>
       </c>
       <c r="T20">
-        <v>0.6151455396283916</v>
+        <v>0.6227399290065199</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.422081944216719</v>
+        <v>8.926182894521105</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1061507046842839</v>
+        <v>0.1062277046842839</v>
       </c>
       <c r="C21">
-        <v>99.20533629909097</v>
+        <v>98.15610807011302</v>
       </c>
       <c r="D21">
-        <v>107.693336299091</v>
+        <v>107.556108070113</v>
       </c>
       <c r="E21">
-        <v>-12.872</v>
+        <v>-11.96</v>
       </c>
       <c r="F21">
-        <v>17.328</v>
+        <v>18.24</v>
       </c>
       <c r="G21">
         <v>8.84</v>
@@ -3009,28 +3009,28 @@
         <v>8.275</v>
       </c>
       <c r="M21">
-        <v>0.927048</v>
+        <v>0.97584</v>
       </c>
       <c r="N21">
-        <v>7.347952</v>
+        <v>7.299160000000001</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>7.347952</v>
+        <v>7.299160000000001</v>
       </c>
       <c r="Q21">
-        <v>8.947952000000001</v>
+        <v>8.89916</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1185008699805974</v>
+        <v>0.1194096308553548</v>
       </c>
       <c r="T21">
-        <v>0.6227399290065199</v>
+        <v>0.6305241781191013</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.926182894521105</v>
+        <v>8.479873749795049</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1062277046842839</v>
+        <v>0.1063047046842839</v>
       </c>
       <c r="C22">
-        <v>98.15610807011302</v>
+        <v>97.10722912219295</v>
       </c>
       <c r="D22">
-        <v>107.556108070113</v>
+        <v>107.4192291221929</v>
       </c>
       <c r="E22">
-        <v>-11.96</v>
+        <v>-11.048</v>
       </c>
       <c r="F22">
-        <v>18.24</v>
+        <v>19.152</v>
       </c>
       <c r="G22">
         <v>8.84</v>
@@ -3091,28 +3091,28 @@
         <v>8.275</v>
       </c>
       <c r="M22">
-        <v>0.97584</v>
+        <v>1.024632</v>
       </c>
       <c r="N22">
-        <v>7.299160000000001</v>
+        <v>7.250368</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>7.299160000000001</v>
+        <v>7.250368</v>
       </c>
       <c r="Q22">
-        <v>8.89916</v>
+        <v>8.850368</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1194096308553548</v>
+        <v>0.1203413983345366</v>
       </c>
       <c r="T22">
-        <v>0.6305241781191013</v>
+        <v>0.6385054968294698</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.479873749795049</v>
+        <v>8.076070237900046</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1063047046842839</v>
+        <v>0.1063817046842839</v>
       </c>
       <c r="C23">
-        <v>97.10722912219295</v>
+        <v>96.05869812351088</v>
       </c>
       <c r="D23">
-        <v>107.4192291221929</v>
+        <v>107.2826981235109</v>
       </c>
       <c r="E23">
-        <v>-11.048</v>
+        <v>-10.136</v>
       </c>
       <c r="F23">
-        <v>19.152</v>
+        <v>20.064</v>
       </c>
       <c r="G23">
         <v>8.84</v>
@@ -3173,28 +3173,28 @@
         <v>8.275</v>
       </c>
       <c r="M23">
-        <v>1.024632</v>
+        <v>1.073424</v>
       </c>
       <c r="N23">
-        <v>7.250368</v>
+        <v>7.201576</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>7.250368</v>
+        <v>7.201576</v>
       </c>
       <c r="Q23">
-        <v>8.850368</v>
+        <v>8.801576000000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1203413983345366</v>
+        <v>0.1212970572875434</v>
       </c>
       <c r="T23">
-        <v>0.6385054968294698</v>
+        <v>0.6466914647375398</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.076070237900046</v>
+        <v>7.708976136177317</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1063817046842839</v>
+        <v>0.1066427046842839</v>
       </c>
       <c r="C24">
-        <v>96.05869812351088</v>
+        <v>94.68648215586884</v>
       </c>
       <c r="D24">
-        <v>107.2826981235109</v>
+        <v>106.8224821558688</v>
       </c>
       <c r="E24">
-        <v>-10.136</v>
+        <v>-9.223999999999997</v>
       </c>
       <c r="F24">
-        <v>20.064</v>
+        <v>20.976</v>
       </c>
       <c r="G24">
         <v>8.84</v>
@@ -3255,45 +3255,45 @@
         <v>8.275</v>
       </c>
       <c r="M24">
-        <v>1.073424</v>
+        <v>1.1389968</v>
       </c>
       <c r="N24">
-        <v>7.201576</v>
+        <v>7.1360032</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>7.201576</v>
+        <v>7.1360032</v>
       </c>
       <c r="Q24">
-        <v>8.801576000000001</v>
+        <v>8.736003200000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1212970572875434</v>
+        <v>0.122277538551018</v>
       </c>
       <c r="T24">
-        <v>0.6466914647375398</v>
+        <v>0.6550900551886767</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.708976136177317</v>
+        <v>7.265165275266796</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1066427046842839</v>
+        <v>0.1067277046842839</v>
       </c>
       <c r="C25">
-        <v>94.68648215586884</v>
+        <v>93.62545453320848</v>
       </c>
       <c r="D25">
-        <v>106.8224821558688</v>
+        <v>106.6734545332085</v>
       </c>
       <c r="E25">
-        <v>-9.223999999999997</v>
+        <v>-8.311999999999998</v>
       </c>
       <c r="F25">
-        <v>20.976</v>
+        <v>21.888</v>
       </c>
       <c r="G25">
         <v>8.84</v>
@@ -3337,28 +3337,28 @@
         <v>8.275</v>
       </c>
       <c r="M25">
-        <v>1.1389968</v>
+        <v>1.1885184</v>
       </c>
       <c r="N25">
-        <v>7.1360032</v>
+        <v>7.0864816</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>7.1360032</v>
+        <v>7.0864816</v>
       </c>
       <c r="Q25">
-        <v>8.736003200000001</v>
+        <v>8.6864816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.122277538551018</v>
+        <v>0.1232838219530051</v>
       </c>
       <c r="T25">
-        <v>0.6550900551886767</v>
+        <v>0.6637096611780015</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.265165275266796</v>
+        <v>6.962450055464012</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1067277046842839</v>
+        <v>0.1068127046842839</v>
       </c>
       <c r="C26">
-        <v>93.62545453320848</v>
+        <v>92.56484214694827</v>
       </c>
       <c r="D26">
-        <v>106.6734545332085</v>
+        <v>106.5248421469483</v>
       </c>
       <c r="E26">
-        <v>-8.312000000000001</v>
+        <v>-7.399999999999999</v>
       </c>
       <c r="F26">
-        <v>21.888</v>
+        <v>22.8</v>
       </c>
       <c r="G26">
         <v>8.84</v>
@@ -3419,28 +3419,28 @@
         <v>8.275</v>
       </c>
       <c r="M26">
-        <v>1.1885184</v>
+        <v>1.23804</v>
       </c>
       <c r="N26">
-        <v>7.086481600000001</v>
+        <v>7.036960000000001</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>7.086481600000001</v>
+        <v>7.036960000000001</v>
       </c>
       <c r="Q26">
-        <v>8.6864816</v>
+        <v>8.63696</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1232838219530051</v>
+        <v>0.1243169395790452</v>
       </c>
       <c r="T26">
-        <v>0.6637096611780015</v>
+        <v>0.6725591233270414</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.962450055464013</v>
+        <v>6.683952053245453</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1068127046842839</v>
+        <v>0.1068977046842839</v>
       </c>
       <c r="C27">
-        <v>92.56484214694827</v>
+        <v>91.50464326403966</v>
       </c>
       <c r="D27">
-        <v>106.5248421469483</v>
+        <v>106.3766432640397</v>
       </c>
       <c r="E27">
-        <v>-7.399999999999999</v>
+        <v>-6.487999999999996</v>
       </c>
       <c r="F27">
-        <v>22.8</v>
+        <v>23.712</v>
       </c>
       <c r="G27">
         <v>8.84</v>
@@ -3501,28 +3501,28 @@
         <v>8.275</v>
       </c>
       <c r="M27">
-        <v>1.23804</v>
+        <v>1.2875616</v>
       </c>
       <c r="N27">
-        <v>7.036960000000001</v>
+        <v>6.9874384</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>7.036960000000001</v>
+        <v>6.9874384</v>
       </c>
       <c r="Q27">
-        <v>8.63696</v>
+        <v>8.5874384</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1243169395790452</v>
+        <v>0.1253779793030863</v>
       </c>
       <c r="T27">
-        <v>0.6725591233270414</v>
+        <v>0.6816477601287582</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.683952053245453</v>
+        <v>6.426876974274473</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1068977046842839</v>
+        <v>0.1069827046842839</v>
       </c>
       <c r="C28">
-        <v>91.50464326403966</v>
+        <v>90.44485616106499</v>
       </c>
       <c r="D28">
-        <v>106.3766432640397</v>
+        <v>106.228856161065</v>
       </c>
       <c r="E28">
-        <v>-6.487999999999996</v>
+        <v>-5.575999999999997</v>
       </c>
       <c r="F28">
-        <v>23.712</v>
+        <v>24.624</v>
       </c>
       <c r="G28">
         <v>8.84</v>
@@ -3583,28 +3583,28 @@
         <v>8.275</v>
       </c>
       <c r="M28">
-        <v>1.2875616</v>
+        <v>1.3370832</v>
       </c>
       <c r="N28">
-        <v>6.9874384</v>
+        <v>6.9379168</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>6.9874384</v>
+        <v>6.9379168</v>
       </c>
       <c r="Q28">
-        <v>8.5874384</v>
+        <v>8.5379168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1253779793030863</v>
+        <v>0.1264680886086081</v>
       </c>
       <c r="T28">
-        <v>0.6816477601287582</v>
+        <v>0.6909854006784674</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.426876974274473</v>
+        <v>6.188844493745789</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1069827046842839</v>
+        <v>0.1073477046842839</v>
       </c>
       <c r="C29">
-        <v>90.44485616106499</v>
+        <v>88.90288088095211</v>
       </c>
       <c r="D29">
-        <v>106.228856161065</v>
+        <v>105.5988808809521</v>
       </c>
       <c r="E29">
-        <v>-5.575999999999997</v>
+        <v>-4.663999999999994</v>
       </c>
       <c r="F29">
-        <v>24.624</v>
+        <v>25.536</v>
       </c>
       <c r="G29">
         <v>8.84</v>
@@ -3665,45 +3665,45 @@
         <v>8.275</v>
       </c>
       <c r="M29">
-        <v>1.3370832</v>
+        <v>1.4121408</v>
       </c>
       <c r="N29">
-        <v>6.9379168</v>
+        <v>6.8628592</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>6.9379168</v>
+        <v>6.8628592</v>
       </c>
       <c r="Q29">
-        <v>8.5379168</v>
+        <v>8.4628592</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1264680886086081</v>
+        <v>0.1275884787281721</v>
       </c>
       <c r="T29">
-        <v>0.6909854006784674</v>
+        <v>0.7005824201323348</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.188844493745789</v>
+        <v>5.859897256704146</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1073477046842839</v>
+        <v>0.1074427046842839</v>
       </c>
       <c r="C30">
-        <v>88.90288088095211</v>
+        <v>87.82813828659205</v>
       </c>
       <c r="D30">
-        <v>105.5988808809521</v>
+        <v>105.4361382865921</v>
       </c>
       <c r="E30">
-        <v>-4.663999999999994</v>
+        <v>-3.751999999999995</v>
       </c>
       <c r="F30">
-        <v>25.536</v>
+        <v>26.448</v>
       </c>
       <c r="G30">
         <v>8.84</v>
@@ -3747,28 +3747,28 @@
         <v>8.275</v>
       </c>
       <c r="M30">
-        <v>1.4121408</v>
+        <v>1.4625744</v>
       </c>
       <c r="N30">
-        <v>6.8628592</v>
+        <v>6.8124256</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>6.8628592</v>
+        <v>6.8124256</v>
       </c>
       <c r="Q30">
-        <v>8.4628592</v>
+        <v>8.412425600000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1275884787281721</v>
+        <v>0.1287404291327942</v>
       </c>
       <c r="T30">
-        <v>0.7005824201323348</v>
+        <v>0.7104497781623678</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.859897256704146</v>
+        <v>5.657831834059176</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1074427046842839</v>
+        <v>0.1075377046842839</v>
       </c>
       <c r="C31">
-        <v>87.82813828659206</v>
+        <v>86.75389653840192</v>
       </c>
       <c r="D31">
-        <v>105.4361382865921</v>
+        <v>105.2738965384019</v>
       </c>
       <c r="E31">
-        <v>-3.751999999999999</v>
+        <v>-2.84</v>
       </c>
       <c r="F31">
-        <v>26.448</v>
+        <v>27.36</v>
       </c>
       <c r="G31">
         <v>8.84</v>
@@ -3829,28 +3829,28 @@
         <v>8.275</v>
       </c>
       <c r="M31">
-        <v>1.4625744</v>
+        <v>1.513008</v>
       </c>
       <c r="N31">
-        <v>6.8124256</v>
+        <v>6.761992</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>6.8124256</v>
+        <v>6.761992</v>
       </c>
       <c r="Q31">
-        <v>8.412425600000001</v>
+        <v>8.361992000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1287404291327942</v>
+        <v>0.1299252924061198</v>
       </c>
       <c r="T31">
-        <v>0.7104497781623677</v>
+        <v>0.7205990607075444</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.657831834059176</v>
+        <v>5.469237439590537</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1075377046842839</v>
+        <v>0.1076327046842839</v>
       </c>
       <c r="C32">
-        <v>86.75389653840192</v>
+        <v>85.68015332787579</v>
       </c>
       <c r="D32">
-        <v>105.2738965384019</v>
+        <v>105.1121533278758</v>
       </c>
       <c r="E32">
-        <v>-2.84</v>
+        <v>-1.927999999999997</v>
       </c>
       <c r="F32">
-        <v>27.36</v>
+        <v>28.272</v>
       </c>
       <c r="G32">
         <v>8.84</v>
@@ -3911,28 +3911,28 @@
         <v>8.275</v>
       </c>
       <c r="M32">
-        <v>1.513008</v>
+        <v>1.5634416</v>
       </c>
       <c r="N32">
-        <v>6.761992</v>
+        <v>6.7115584</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>6.761992</v>
+        <v>6.7115584</v>
       </c>
       <c r="Q32">
-        <v>8.361992000000001</v>
+        <v>8.311558400000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1299252924061198</v>
+        <v>0.1311444995424404</v>
       </c>
       <c r="T32">
-        <v>0.7205990607075444</v>
+        <v>0.7310425253554799</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.469237439590537</v>
+        <v>5.292810425410197</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1076327046842839</v>
+        <v>0.1077277046842839</v>
       </c>
       <c r="C33">
-        <v>85.68015332787579</v>
+        <v>84.60690636067338</v>
       </c>
       <c r="D33">
-        <v>105.1121533278758</v>
+        <v>104.9509063606734</v>
       </c>
       <c r="E33">
-        <v>-1.927999999999997</v>
+        <v>-1.015999999999998</v>
       </c>
       <c r="F33">
-        <v>28.272</v>
+        <v>29.184</v>
       </c>
       <c r="G33">
         <v>8.84</v>
@@ -3993,28 +3993,28 @@
         <v>8.275</v>
       </c>
       <c r="M33">
-        <v>1.5634416</v>
+        <v>1.6138752</v>
       </c>
       <c r="N33">
-        <v>6.7115584</v>
+        <v>6.661124800000001</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>6.7115584</v>
+        <v>6.661124800000001</v>
       </c>
       <c r="Q33">
-        <v>8.311558400000001</v>
+        <v>8.261124800000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1311444995424404</v>
+        <v>0.1323995657121822</v>
       </c>
       <c r="T33">
-        <v>0.7310425253554799</v>
+        <v>0.7417931507283546</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.292810425410197</v>
+        <v>5.127410099616129</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1077277046842839</v>
+        <v>0.1078227046842839</v>
       </c>
       <c r="C34">
-        <v>84.60690636067338</v>
+        <v>83.53415335651118</v>
       </c>
       <c r="D34">
-        <v>104.9509063606734</v>
+        <v>104.7901533565112</v>
       </c>
       <c r="E34">
-        <v>-1.015999999999998</v>
+        <v>-0.1039999999999957</v>
       </c>
       <c r="F34">
-        <v>29.184</v>
+        <v>30.096</v>
       </c>
       <c r="G34">
         <v>8.84</v>
@@ -4075,28 +4075,28 @@
         <v>8.275</v>
       </c>
       <c r="M34">
-        <v>1.6138752</v>
+        <v>1.6643088</v>
       </c>
       <c r="N34">
-        <v>6.661124800000001</v>
+        <v>6.6106912</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>6.661124800000001</v>
+        <v>6.6106912</v>
       </c>
       <c r="Q34">
-        <v>8.261124800000001</v>
+        <v>8.210691199999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1323995657121822</v>
+        <v>0.1336920965437073</v>
       </c>
       <c r="T34">
-        <v>0.7417931507283546</v>
+        <v>0.7528646902914643</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.127410099616129</v>
+        <v>4.972034035991397</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1078227046842839</v>
+        <v>0.1079177046842839</v>
       </c>
       <c r="C35">
-        <v>83.53415335651118</v>
+        <v>82.46189204905517</v>
       </c>
       <c r="D35">
-        <v>104.7901533565112</v>
+        <v>104.6298920490552</v>
       </c>
       <c r="E35">
-        <v>-0.1039999999999957</v>
+        <v>0.8080000000000034</v>
       </c>
       <c r="F35">
-        <v>30.096</v>
+        <v>31.008</v>
       </c>
       <c r="G35">
         <v>8.84</v>
@@ -4157,28 +4157,28 @@
         <v>8.275</v>
       </c>
       <c r="M35">
-        <v>1.6643088</v>
+        <v>1.7147424</v>
       </c>
       <c r="N35">
-        <v>6.6106912</v>
+        <v>6.5602576</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>6.6106912</v>
+        <v>6.5602576</v>
       </c>
       <c r="Q35">
-        <v>8.210691199999999</v>
+        <v>8.1602576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1336920965437073</v>
+        <v>0.1350237949761877</v>
       </c>
       <c r="T35">
-        <v>0.7528646902914643</v>
+        <v>0.7642717310534561</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.972034035991397</v>
+        <v>4.82579774081518</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1079177046842839</v>
+        <v>0.1080127046842839</v>
       </c>
       <c r="C36">
-        <v>82.46189204905517</v>
+        <v>81.39012018581434</v>
       </c>
       <c r="D36">
-        <v>104.6298920490552</v>
+        <v>104.4701201858143</v>
       </c>
       <c r="E36">
-        <v>0.8080000000000034</v>
+        <v>1.720000000000006</v>
       </c>
       <c r="F36">
-        <v>31.008</v>
+        <v>31.92000000000001</v>
       </c>
       <c r="G36">
         <v>8.84</v>
@@ -4239,28 +4239,28 @@
         <v>8.275</v>
       </c>
       <c r="M36">
-        <v>1.7147424</v>
+        <v>1.765176</v>
       </c>
       <c r="N36">
-        <v>6.5602576</v>
+        <v>6.509824</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>6.5602576</v>
+        <v>6.509824</v>
       </c>
       <c r="Q36">
-        <v>8.1602576</v>
+        <v>8.109824</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1350237949761877</v>
+        <v>0.1363964687450521</v>
       </c>
       <c r="T36">
-        <v>0.7642717310534561</v>
+        <v>0.7760297576850479</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.82579774081518</v>
+        <v>4.687917805363318</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1080127046842839</v>
+        <v>0.1081077046842839</v>
       </c>
       <c r="C37">
-        <v>81.39012018581434</v>
+        <v>80.31883552803502</v>
       </c>
       <c r="D37">
-        <v>104.4701201858143</v>
+        <v>104.310835528035</v>
       </c>
       <c r="E37">
-        <v>1.720000000000006</v>
+        <v>2.632000000000009</v>
       </c>
       <c r="F37">
-        <v>31.92000000000001</v>
+        <v>32.83200000000001</v>
       </c>
       <c r="G37">
         <v>8.84</v>
@@ -4321,28 +4321,28 @@
         <v>8.275</v>
       </c>
       <c r="M37">
-        <v>1.765176</v>
+        <v>1.815609600000001</v>
       </c>
       <c r="N37">
-        <v>6.509824</v>
+        <v>6.4593904</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>6.509824</v>
+        <v>6.4593904</v>
       </c>
       <c r="Q37">
-        <v>8.109824</v>
+        <v>8.0593904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1363964687450521</v>
+        <v>0.1378120385691936</v>
       </c>
       <c r="T37">
-        <v>0.7760297576850479</v>
+        <v>0.7881552226488767</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.687917805363318</v>
+        <v>4.557697866325447</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1081077046842839</v>
+        <v>0.1091277046842839</v>
       </c>
       <c r="C38">
-        <v>80.31883552803501</v>
+        <v>77.72673275518017</v>
       </c>
       <c r="D38">
-        <v>104.310835528035</v>
+        <v>102.6307327551802</v>
       </c>
       <c r="E38">
-        <v>2.632000000000001</v>
+        <v>3.544</v>
       </c>
       <c r="F38">
-        <v>32.832</v>
+        <v>33.744</v>
       </c>
       <c r="G38">
         <v>8.84</v>
@@ -4403,45 +4403,45 @@
         <v>8.275</v>
       </c>
       <c r="M38">
-        <v>1.8156096</v>
+        <v>1.9504032</v>
       </c>
       <c r="N38">
-        <v>6.4593904</v>
+        <v>6.3245968</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>6.4593904</v>
+        <v>6.3245968</v>
       </c>
       <c r="Q38">
-        <v>8.0593904</v>
+        <v>7.9245968</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1378120385691936</v>
+        <v>0.1392725471179109</v>
       </c>
       <c r="T38">
-        <v>0.7881552226488767</v>
+        <v>0.8006656230083827</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.557697866325448</v>
+        <v>4.242712481193632</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1091277046842839</v>
+        <v>0.1092477046842839</v>
       </c>
       <c r="C39">
-        <v>77.72673275518017</v>
+        <v>76.62062505669206</v>
       </c>
       <c r="D39">
-        <v>102.6307327551802</v>
+        <v>102.4366250566921</v>
       </c>
       <c r="E39">
-        <v>3.544</v>
+        <v>4.456</v>
       </c>
       <c r="F39">
-        <v>33.744</v>
+        <v>34.656</v>
       </c>
       <c r="G39">
         <v>8.84</v>
@@ -4485,28 +4485,28 @@
         <v>8.275</v>
       </c>
       <c r="M39">
-        <v>1.9504032</v>
+        <v>2.0031168</v>
       </c>
       <c r="N39">
-        <v>6.3245968</v>
+        <v>6.2718832</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>6.3245968</v>
+        <v>6.2718832</v>
       </c>
       <c r="Q39">
-        <v>7.9245968</v>
+        <v>7.871883200000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1392725471179109</v>
+        <v>0.1407801688456191</v>
       </c>
       <c r="T39">
-        <v>0.8006656230083827</v>
+        <v>0.8135795846698082</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.242712481193632</v>
+        <v>4.131062152741169</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1092477046842839</v>
+        <v>0.1093677046842839</v>
       </c>
       <c r="C40">
-        <v>76.62062505669206</v>
+        <v>75.51525021221943</v>
       </c>
       <c r="D40">
-        <v>102.4366250566921</v>
+        <v>102.2432502122194</v>
       </c>
       <c r="E40">
-        <v>4.456</v>
+        <v>5.368000000000006</v>
       </c>
       <c r="F40">
-        <v>34.656</v>
+        <v>35.568</v>
       </c>
       <c r="G40">
         <v>8.84</v>
@@ -4567,28 +4567,28 @@
         <v>8.275</v>
       </c>
       <c r="M40">
-        <v>2.0031168</v>
+        <v>2.055830400000001</v>
       </c>
       <c r="N40">
-        <v>6.2718832</v>
+        <v>6.2191696</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>6.2718832</v>
+        <v>6.2191696</v>
       </c>
       <c r="Q40">
-        <v>7.871883200000001</v>
+        <v>7.8191696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1407801688456191</v>
+        <v>0.142337220793908</v>
       </c>
       <c r="T40">
-        <v>0.8135795846698082</v>
+        <v>0.8269169549102969</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.131062152741169</v>
+        <v>4.02513748215806</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1093677046842839</v>
+        <v>0.1108877046842839</v>
       </c>
       <c r="C41">
-        <v>75.51525021221943</v>
+        <v>72.21555285714436</v>
       </c>
       <c r="D41">
-        <v>102.2432502122194</v>
+        <v>99.85555285714436</v>
       </c>
       <c r="E41">
-        <v>5.368000000000006</v>
+        <v>6.280000000000005</v>
       </c>
       <c r="F41">
-        <v>35.568</v>
+        <v>36.48</v>
       </c>
       <c r="G41">
         <v>8.84</v>
@@ -4649,45 +4649,45 @@
         <v>8.275</v>
       </c>
       <c r="M41">
-        <v>2.055830400000001</v>
+        <v>2.236224</v>
       </c>
       <c r="N41">
-        <v>6.2191696</v>
+        <v>6.038776</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>6.2191696</v>
+        <v>6.038776</v>
       </c>
       <c r="Q41">
-        <v>7.8191696</v>
+        <v>7.638776</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.142337220793908</v>
+        <v>0.1439461744738065</v>
       </c>
       <c r="T41">
-        <v>0.8269169549102969</v>
+        <v>0.8406989041588019</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.02513748215806</v>
+        <v>3.700434303540253</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1108877046842839</v>
+        <v>0.1110427046842839</v>
       </c>
       <c r="C42">
-        <v>72.21555285714436</v>
+        <v>71.06632157178063</v>
       </c>
       <c r="D42">
-        <v>99.85555285714436</v>
+        <v>99.61832157178064</v>
       </c>
       <c r="E42">
-        <v>6.280000000000005</v>
+        <v>7.192000000000004</v>
       </c>
       <c r="F42">
-        <v>36.48</v>
+        <v>37.392</v>
       </c>
       <c r="G42">
         <v>8.84</v>
@@ -4731,28 +4731,28 @@
         <v>8.275</v>
       </c>
       <c r="M42">
-        <v>2.236224</v>
+        <v>2.2921296</v>
       </c>
       <c r="N42">
-        <v>6.038776</v>
+        <v>5.9828704</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>6.038776</v>
+        <v>5.9828704</v>
       </c>
       <c r="Q42">
-        <v>7.638776</v>
+        <v>7.582870400000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1439461744738065</v>
+        <v>0.1456096689564133</v>
       </c>
       <c r="T42">
-        <v>0.8406989041588019</v>
+        <v>0.854948038127595</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.700434303540253</v>
+        <v>3.610179808331955</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1110427046842839</v>
+        <v>0.1111977046842839</v>
       </c>
       <c r="C43">
-        <v>71.06632157178063</v>
+        <v>69.91821481668627</v>
       </c>
       <c r="D43">
-        <v>99.61832157178064</v>
+        <v>99.38221481668627</v>
       </c>
       <c r="E43">
-        <v>7.192000000000004</v>
+        <v>8.104000000000003</v>
       </c>
       <c r="F43">
-        <v>37.392</v>
+        <v>38.304</v>
       </c>
       <c r="G43">
         <v>8.84</v>
@@ -4813,28 +4813,28 @@
         <v>8.275</v>
       </c>
       <c r="M43">
-        <v>2.2921296</v>
+        <v>2.3480352</v>
       </c>
       <c r="N43">
-        <v>5.9828704</v>
+        <v>5.9269648</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>5.9828704</v>
+        <v>5.9269648</v>
       </c>
       <c r="Q43">
-        <v>7.582870400000001</v>
+        <v>7.5269648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1456096689564133</v>
+        <v>0.1473305253177308</v>
       </c>
       <c r="T43">
-        <v>0.854948038127595</v>
+        <v>0.8696885215435881</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.610179808331955</v>
+        <v>3.524223146228813</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1111977046842839</v>
+        <v>0.1125567046842839</v>
       </c>
       <c r="C44">
-        <v>69.91821481668627</v>
+        <v>66.98304080630595</v>
       </c>
       <c r="D44">
-        <v>99.38221481668627</v>
+        <v>97.35904080630596</v>
       </c>
       <c r="E44">
-        <v>8.104000000000003</v>
+        <v>9.016000000000002</v>
       </c>
       <c r="F44">
-        <v>38.304</v>
+        <v>39.216</v>
       </c>
       <c r="G44">
         <v>8.84</v>
@@ -4895,45 +4895,45 @@
         <v>8.275</v>
       </c>
       <c r="M44">
-        <v>2.3480352</v>
+        <v>2.5137456</v>
       </c>
       <c r="N44">
-        <v>5.9269648</v>
+        <v>5.7612544</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>5.9269648</v>
+        <v>5.7612544</v>
       </c>
       <c r="Q44">
-        <v>7.5269648</v>
+        <v>7.3612544</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1473305253177308</v>
+        <v>0.1491117626040068</v>
       </c>
       <c r="T44">
-        <v>0.869688521543588</v>
+        <v>0.8849462149040018</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.524223146228813</v>
+        <v>3.291900341864348</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1125567046842839</v>
+        <v>0.1127397046842839</v>
       </c>
       <c r="C45">
-        <v>66.98304080630595</v>
+        <v>65.80488031827294</v>
       </c>
       <c r="D45">
-        <v>97.35904080630596</v>
+        <v>97.09288031827293</v>
       </c>
       <c r="E45">
-        <v>9.016000000000002</v>
+        <v>9.928000000000001</v>
       </c>
       <c r="F45">
-        <v>39.216</v>
+        <v>40.128</v>
       </c>
       <c r="G45">
         <v>8.84</v>
@@ -4977,28 +4977,28 @@
         <v>8.275</v>
       </c>
       <c r="M45">
-        <v>2.5137456</v>
+        <v>2.5722048</v>
       </c>
       <c r="N45">
-        <v>5.7612544</v>
+        <v>5.702795200000001</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>5.7612544</v>
+        <v>5.702795200000001</v>
       </c>
       <c r="Q45">
-        <v>7.3612544</v>
+        <v>7.3027952</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1491117626040068</v>
+        <v>0.1509566155076498</v>
       </c>
       <c r="T45">
-        <v>0.8849462149040018</v>
+        <v>0.9007488258844304</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.291900341864348</v>
+        <v>3.217084425003795</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1127397046842839</v>
+        <v>0.1129227046842839</v>
       </c>
       <c r="C46">
-        <v>65.80488031827294</v>
+        <v>64.62817112364473</v>
       </c>
       <c r="D46">
-        <v>97.09288031827293</v>
+        <v>96.82817112364474</v>
       </c>
       <c r="E46">
-        <v>9.928000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="F46">
-        <v>40.128</v>
+        <v>41.04</v>
       </c>
       <c r="G46">
         <v>8.84</v>
@@ -5059,28 +5059,28 @@
         <v>8.275</v>
       </c>
       <c r="M46">
-        <v>2.5722048</v>
+        <v>2.630664</v>
       </c>
       <c r="N46">
-        <v>5.702795200000001</v>
+        <v>5.644336</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>5.702795200000001</v>
+        <v>5.644336</v>
       </c>
       <c r="Q46">
-        <v>7.3027952</v>
+        <v>7.244336000000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1509566155076498</v>
+        <v>0.1528685539714252</v>
       </c>
       <c r="T46">
-        <v>0.9007488258844304</v>
+        <v>0.9171260772641474</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.217084425003795</v>
+        <v>3.14559366000371</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1129227046842839</v>
+        <v>0.1131057046842839</v>
       </c>
       <c r="C47">
-        <v>64.62817112364473</v>
+        <v>63.45290138449345</v>
       </c>
       <c r="D47">
-        <v>96.82817112364474</v>
+        <v>96.56490138449345</v>
       </c>
       <c r="E47">
-        <v>10.84</v>
+        <v>11.75200000000001</v>
       </c>
       <c r="F47">
-        <v>41.04</v>
+        <v>41.95200000000001</v>
       </c>
       <c r="G47">
         <v>8.84</v>
@@ -5141,28 +5141,28 @@
         <v>8.275</v>
       </c>
       <c r="M47">
-        <v>2.630664</v>
+        <v>2.6891232</v>
       </c>
       <c r="N47">
-        <v>5.644336</v>
+        <v>5.585876799999999</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>5.644336</v>
+        <v>5.585876799999999</v>
       </c>
       <c r="Q47">
-        <v>7.244336000000001</v>
+        <v>7.185876799999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1528685539714252</v>
+        <v>0.1548513049708961</v>
       </c>
       <c r="T47">
-        <v>0.9171260772641474</v>
+        <v>0.9341098935097798</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.14559366000371</v>
+        <v>3.077211189134064</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1131057046842839</v>
+        <v>0.1132887046842839</v>
       </c>
       <c r="C48">
-        <v>63.45290138449345</v>
+        <v>62.27905939128834</v>
       </c>
       <c r="D48">
-        <v>96.56490138449345</v>
+        <v>96.30305939128834</v>
       </c>
       <c r="E48">
-        <v>11.75200000000001</v>
+        <v>12.66400000000001</v>
       </c>
       <c r="F48">
-        <v>41.95200000000001</v>
+        <v>42.864</v>
       </c>
       <c r="G48">
         <v>8.84</v>
@@ -5223,28 +5223,28 @@
         <v>8.275</v>
       </c>
       <c r="M48">
-        <v>2.6891232</v>
+        <v>2.747582400000001</v>
       </c>
       <c r="N48">
-        <v>5.585876799999999</v>
+        <v>5.5274176</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>5.585876799999999</v>
+        <v>5.5274176</v>
       </c>
       <c r="Q48">
-        <v>7.185876799999999</v>
+        <v>7.127417599999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1548513049708961</v>
+        <v>0.1569088767627998</v>
       </c>
       <c r="T48">
-        <v>0.9341098935097798</v>
+        <v>0.9517346084816625</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.077211189134064</v>
+        <v>3.011738610641849</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1132887046842839</v>
+        <v>0.1172157046842839</v>
       </c>
       <c r="C49">
-        <v>62.27905939128834</v>
+        <v>56.07155588962208</v>
       </c>
       <c r="D49">
-        <v>96.30305939128834</v>
+        <v>91.00755588962208</v>
       </c>
       <c r="E49">
-        <v>12.66400000000001</v>
+        <v>13.576</v>
       </c>
       <c r="F49">
-        <v>42.864</v>
+        <v>43.776</v>
       </c>
       <c r="G49">
         <v>8.84</v>
@@ -5305,45 +5305,45 @@
         <v>8.275</v>
       </c>
       <c r="M49">
-        <v>2.747582400000001</v>
+        <v>3.147494400000001</v>
       </c>
       <c r="N49">
-        <v>5.5274176</v>
+        <v>5.127505599999999</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>5.5274176</v>
+        <v>5.127505599999999</v>
       </c>
       <c r="Q49">
-        <v>7.127417599999999</v>
+        <v>6.727505599999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1569088767627998</v>
+        <v>0.1590455859313152</v>
       </c>
       <c r="T49">
-        <v>0.9517346084816625</v>
+        <v>0.9700371971063098</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.011738610641849</v>
+        <v>2.629075368648789</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1172157046842839</v>
+        <v>0.1174767046842839</v>
       </c>
       <c r="C50">
-        <v>56.0715558896221</v>
+        <v>54.82816548611764</v>
       </c>
       <c r="D50">
-        <v>91.0075558896221</v>
+        <v>90.67616548611764</v>
       </c>
       <c r="E50">
-        <v>13.576</v>
+        <v>14.488</v>
       </c>
       <c r="F50">
-        <v>43.776</v>
+        <v>44.688</v>
       </c>
       <c r="G50">
         <v>8.84</v>
@@ -5387,28 +5387,28 @@
         <v>8.275</v>
       </c>
       <c r="M50">
-        <v>3.1474944</v>
+        <v>3.2130672</v>
       </c>
       <c r="N50">
-        <v>5.127505600000001</v>
+        <v>5.0619328</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>5.127505600000001</v>
+        <v>5.0619328</v>
       </c>
       <c r="Q50">
-        <v>6.727505600000001</v>
+        <v>6.661932800000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1590455859313151</v>
+        <v>0.1612660876162429</v>
       </c>
       <c r="T50">
-        <v>0.9700371971063096</v>
+        <v>0.9890575343044726</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.62907536864879</v>
+        <v>2.57542076928861</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1174767046842839</v>
+        <v>0.1177377046842839</v>
       </c>
       <c r="C51">
-        <v>54.82816548611764</v>
+        <v>53.58717974358192</v>
       </c>
       <c r="D51">
-        <v>90.67616548611764</v>
+        <v>90.34717974358192</v>
       </c>
       <c r="E51">
-        <v>14.488</v>
+        <v>15.4</v>
       </c>
       <c r="F51">
-        <v>44.688</v>
+        <v>45.6</v>
       </c>
       <c r="G51">
         <v>8.84</v>
@@ -5469,28 +5469,28 @@
         <v>8.275</v>
       </c>
       <c r="M51">
-        <v>3.2130672</v>
+        <v>3.27864</v>
       </c>
       <c r="N51">
-        <v>5.0619328</v>
+        <v>4.99636</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>5.0619328</v>
+        <v>4.99636</v>
       </c>
       <c r="Q51">
-        <v>6.661932800000001</v>
+        <v>6.596360000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1612660876162429</v>
+        <v>0.1635754093685677</v>
       </c>
       <c r="T51">
-        <v>0.9890575343044726</v>
+        <v>1.008838684990562</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.57542076928861</v>
+        <v>2.523912353902838</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1177377046842839</v>
+        <v>0.1199877046842839</v>
       </c>
       <c r="C52">
-        <v>53.58717974358192</v>
+        <v>49.9350874966503</v>
       </c>
       <c r="D52">
-        <v>90.34717974358192</v>
+        <v>87.60708749665029</v>
       </c>
       <c r="E52">
-        <v>15.4</v>
+        <v>16.312</v>
       </c>
       <c r="F52">
-        <v>45.6</v>
+        <v>46.512</v>
       </c>
       <c r="G52">
         <v>8.84</v>
@@ -5551,45 +5551,45 @@
         <v>8.275</v>
       </c>
       <c r="M52">
-        <v>3.27864</v>
+        <v>3.5256096</v>
       </c>
       <c r="N52">
-        <v>4.99636</v>
+        <v>4.7493904</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>4.99636</v>
+        <v>4.7493904</v>
       </c>
       <c r="Q52">
-        <v>6.596360000000001</v>
+        <v>6.349390400000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1635754093685677</v>
+        <v>0.1659789891515997</v>
       </c>
       <c r="T52">
-        <v>1.008838684990562</v>
+        <v>1.029427229582206</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.523912353902838</v>
+        <v>2.347111829965518</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1199877046842839</v>
+        <v>0.1202877046842839</v>
       </c>
       <c r="C53">
-        <v>49.9350874966503</v>
+        <v>48.67024904686328</v>
       </c>
       <c r="D53">
-        <v>87.60708749665029</v>
+        <v>87.25424904686328</v>
       </c>
       <c r="E53">
-        <v>16.312</v>
+        <v>17.22400000000001</v>
       </c>
       <c r="F53">
-        <v>46.512</v>
+        <v>47.42400000000001</v>
       </c>
       <c r="G53">
         <v>8.84</v>
@@ -5633,28 +5633,28 @@
         <v>8.275</v>
       </c>
       <c r="M53">
-        <v>3.5256096</v>
+        <v>3.594739200000001</v>
       </c>
       <c r="N53">
-        <v>4.7493904</v>
+        <v>4.680260799999999</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>4.7493904</v>
+        <v>4.680260799999999</v>
       </c>
       <c r="Q53">
-        <v>6.349390400000001</v>
+        <v>6.280260799999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1659789891515997</v>
+        <v>0.1684827180922581</v>
       </c>
       <c r="T53">
-        <v>1.029427229582206</v>
+        <v>1.050873630198502</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.347111829965518</v>
+        <v>2.301975064004643</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1202877046842839</v>
+        <v>0.1205877046842839</v>
       </c>
       <c r="C54">
-        <v>48.67024904686328</v>
+        <v>47.40824131732324</v>
       </c>
       <c r="D54">
-        <v>87.25424904686328</v>
+        <v>86.90424131732324</v>
       </c>
       <c r="E54">
-        <v>17.22400000000001</v>
+        <v>18.13600000000001</v>
       </c>
       <c r="F54">
-        <v>47.42400000000001</v>
+        <v>48.33600000000001</v>
       </c>
       <c r="G54">
         <v>8.84</v>
@@ -5715,28 +5715,28 @@
         <v>8.275</v>
       </c>
       <c r="M54">
-        <v>3.594739200000001</v>
+        <v>3.663868800000001</v>
       </c>
       <c r="N54">
-        <v>4.680260799999999</v>
+        <v>4.611131199999999</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>4.680260799999999</v>
+        <v>4.611131199999999</v>
       </c>
       <c r="Q54">
-        <v>6.280260799999999</v>
+        <v>6.211131199999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1684827180922581</v>
+        <v>0.1710929886899657</v>
       </c>
       <c r="T54">
-        <v>1.050873630198502</v>
+        <v>1.073232643606981</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.301975064004643</v>
+        <v>2.25854157223097</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1205877046842839</v>
+        <v>0.1208877046842839</v>
       </c>
       <c r="C55">
-        <v>47.40824131732324</v>
+        <v>46.14903037906355</v>
       </c>
       <c r="D55">
-        <v>86.90424131732324</v>
+        <v>86.55703037906355</v>
       </c>
       <c r="E55">
-        <v>18.13600000000001</v>
+        <v>19.04800000000001</v>
       </c>
       <c r="F55">
-        <v>48.33600000000001</v>
+        <v>49.248</v>
       </c>
       <c r="G55">
         <v>8.84</v>
@@ -5797,28 +5797,28 @@
         <v>8.275</v>
       </c>
       <c r="M55">
-        <v>3.663868800000001</v>
+        <v>3.7329984</v>
       </c>
       <c r="N55">
-        <v>4.611131199999999</v>
+        <v>4.5420016</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>4.611131199999999</v>
+        <v>4.5420016</v>
       </c>
       <c r="Q55">
-        <v>6.211131199999999</v>
+        <v>6.1420016</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1710929886899657</v>
+        <v>0.1738167493136606</v>
       </c>
       <c r="T55">
-        <v>1.073232643606981</v>
+        <v>1.09656378803322</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.25854157223097</v>
+        <v>2.216716728300767</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1208877046842839</v>
+        <v>0.1211877046842839</v>
       </c>
       <c r="C56">
-        <v>46.14903037906355</v>
+        <v>44.89258284318927</v>
       </c>
       <c r="D56">
-        <v>86.55703037906355</v>
+        <v>86.21258284318927</v>
       </c>
       <c r="E56">
-        <v>19.04800000000001</v>
+        <v>19.96</v>
       </c>
       <c r="F56">
-        <v>49.248</v>
+        <v>50.16</v>
       </c>
       <c r="G56">
         <v>8.84</v>
@@ -5879,28 +5879,28 @@
         <v>8.275</v>
       </c>
       <c r="M56">
-        <v>3.7329984</v>
+        <v>3.802128000000001</v>
       </c>
       <c r="N56">
-        <v>4.5420016</v>
+        <v>4.472872</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>4.5420016</v>
+        <v>4.472872</v>
       </c>
       <c r="Q56">
-        <v>6.1420016</v>
+        <v>6.072872</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1738167493136606</v>
+        <v>0.1766615659650753</v>
       </c>
       <c r="T56">
-        <v>1.09656378803322</v>
+        <v>1.120931872211736</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.216716728300767</v>
+        <v>2.176412787786208</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1211877046842839</v>
+        <v>0.1214877046842839</v>
       </c>
       <c r="C57">
-        <v>44.89258284318927</v>
+        <v>43.63886585017378</v>
       </c>
       <c r="D57">
-        <v>86.21258284318927</v>
+        <v>85.87086585017379</v>
       </c>
       <c r="E57">
-        <v>19.96</v>
+        <v>20.87200000000001</v>
       </c>
       <c r="F57">
-        <v>50.16</v>
+        <v>51.07200000000001</v>
       </c>
       <c r="G57">
         <v>8.84</v>
@@ -5961,28 +5961,28 @@
         <v>8.275</v>
       </c>
       <c r="M57">
-        <v>3.802128000000001</v>
+        <v>3.871257600000001</v>
       </c>
       <c r="N57">
-        <v>4.472872</v>
+        <v>4.403742399999999</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>4.472872</v>
+        <v>4.403742399999999</v>
       </c>
       <c r="Q57">
-        <v>6.072872</v>
+        <v>6.003742399999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1766615659650753</v>
+        <v>0.1796356924642815</v>
       </c>
       <c r="T57">
-        <v>1.120931872211736</v>
+        <v>1.146407596580184</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.176412787786208</v>
+        <v>2.137548273718597</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1214877046842839</v>
+        <v>0.1217877046842839</v>
       </c>
       <c r="C58">
-        <v>43.63886585017378</v>
+        <v>42.38784705940905</v>
       </c>
       <c r="D58">
-        <v>85.87086585017379</v>
+        <v>85.53184705940906</v>
       </c>
       <c r="E58">
-        <v>20.87200000000001</v>
+        <v>21.78400000000001</v>
       </c>
       <c r="F58">
-        <v>51.07200000000001</v>
+        <v>51.98400000000001</v>
       </c>
       <c r="G58">
         <v>8.84</v>
@@ -6043,28 +6043,28 @@
         <v>8.275</v>
       </c>
       <c r="M58">
-        <v>3.871257600000001</v>
+        <v>3.940387200000001</v>
       </c>
       <c r="N58">
-        <v>4.403742399999999</v>
+        <v>4.334612799999999</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>4.403742399999999</v>
+        <v>4.334612799999999</v>
       </c>
       <c r="Q58">
-        <v>6.003742399999998</v>
+        <v>5.9346128</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1796356924642815</v>
+        <v>0.1827481504285672</v>
       </c>
       <c r="T58">
-        <v>1.146407596580184</v>
+        <v>1.173068238361119</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.137548273718597</v>
+        <v>2.100047426811253</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1217877046842839</v>
+        <v>0.1220877046842839</v>
       </c>
       <c r="C59">
-        <v>42.38784705940905</v>
+        <v>41.13949463900247</v>
       </c>
       <c r="D59">
-        <v>85.53184705940906</v>
+        <v>85.19549463900248</v>
       </c>
       <c r="E59">
-        <v>21.78400000000001</v>
+        <v>22.69600000000001</v>
       </c>
       <c r="F59">
-        <v>51.98400000000001</v>
+        <v>52.89600000000001</v>
       </c>
       <c r="G59">
         <v>8.84</v>
@@ -6125,28 +6125,28 @@
         <v>8.275</v>
       </c>
       <c r="M59">
-        <v>3.940387200000001</v>
+        <v>4.009516800000001</v>
       </c>
       <c r="N59">
-        <v>4.334612799999999</v>
+        <v>4.265483199999999</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>4.334612799999999</v>
+        <v>4.265483199999999</v>
       </c>
       <c r="Q59">
-        <v>5.9346128</v>
+        <v>5.8654832</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1827481504285672</v>
+        <v>0.1860088206768664</v>
       </c>
       <c r="T59">
-        <v>1.173068238361119</v>
+        <v>1.200998434512574</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.100047426811253</v>
+        <v>2.063839712555887</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1220877046842839</v>
+        <v>0.1223877046842839</v>
       </c>
       <c r="C60">
-        <v>41.13949463900248</v>
+        <v>39.89377725581337</v>
       </c>
       <c r="D60">
-        <v>85.19549463900248</v>
+        <v>84.86177725581337</v>
       </c>
       <c r="E60">
-        <v>22.696</v>
+        <v>23.608</v>
       </c>
       <c r="F60">
-        <v>52.896</v>
+        <v>53.808</v>
       </c>
       <c r="G60">
         <v>8.84</v>
@@ -6207,28 +6207,28 @@
         <v>8.275</v>
       </c>
       <c r="M60">
-        <v>4.0095168</v>
+        <v>4.0786464</v>
       </c>
       <c r="N60">
-        <v>4.2654832</v>
+        <v>4.1963536</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>4.2654832</v>
+        <v>4.1963536</v>
       </c>
       <c r="Q60">
-        <v>5.8654832</v>
+        <v>5.7963536</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1860088206768663</v>
+        <v>0.1894285480104484</v>
       </c>
       <c r="T60">
-        <v>1.200998434512574</v>
+        <v>1.230291079256783</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.063839712555887</v>
+        <v>2.02885937844477</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1223877046842839</v>
+        <v>0.1312077046842839</v>
       </c>
       <c r="C61">
-        <v>39.89377725581337</v>
+        <v>30.21815483833835</v>
       </c>
       <c r="D61">
-        <v>84.86177725581337</v>
+        <v>76.09815483833835</v>
       </c>
       <c r="E61">
-        <v>23.608</v>
+        <v>24.52</v>
       </c>
       <c r="F61">
-        <v>53.808</v>
+        <v>54.72</v>
       </c>
       <c r="G61">
         <v>8.84</v>
@@ -6289,45 +6289,45 @@
         <v>8.275</v>
       </c>
       <c r="M61">
-        <v>4.0786464</v>
+        <v>4.924799999999999</v>
       </c>
       <c r="N61">
-        <v>4.1963536</v>
+        <v>3.350200000000001</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>4.1963536</v>
+        <v>3.350200000000001</v>
       </c>
       <c r="Q61">
-        <v>5.7963536</v>
+        <v>4.950200000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1894285480104484</v>
+        <v>0.1930192617107097</v>
       </c>
       <c r="T61">
-        <v>1.230291079256783</v>
+        <v>1.261048356238203</v>
       </c>
       <c r="U61">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.02885937844477</v>
+        <v>1.680271280051982</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1312077046842839</v>
+        <v>0.1316497046842839</v>
       </c>
       <c r="C62">
-        <v>30.21815483833835</v>
+        <v>28.91436101024959</v>
       </c>
       <c r="D62">
-        <v>76.09815483833835</v>
+        <v>75.70636101024958</v>
       </c>
       <c r="E62">
-        <v>24.52</v>
+        <v>25.432</v>
       </c>
       <c r="F62">
-        <v>54.72</v>
+        <v>55.632</v>
       </c>
       <c r="G62">
         <v>8.84</v>
@@ -6371,28 +6371,28 @@
         <v>8.275</v>
       </c>
       <c r="M62">
-        <v>4.924799999999999</v>
+        <v>5.00688</v>
       </c>
       <c r="N62">
-        <v>3.350200000000001</v>
+        <v>3.268120000000001</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>3.350200000000001</v>
+        <v>3.268120000000001</v>
       </c>
       <c r="Q62">
-        <v>4.950200000000001</v>
+        <v>4.868120000000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1930192617107097</v>
+        <v>0.1967941145750869</v>
       </c>
       <c r="T62">
-        <v>1.261048356238203</v>
+        <v>1.29338292947508</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.680271280051982</v>
+        <v>1.652725849231458</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1316497046842839</v>
+        <v>0.1320917046842839</v>
       </c>
       <c r="C63">
-        <v>28.91436101024959</v>
+        <v>27.6145808442538</v>
       </c>
       <c r="D63">
-        <v>75.70636101024958</v>
+        <v>75.3185808442538</v>
       </c>
       <c r="E63">
-        <v>25.432</v>
+        <v>26.344</v>
       </c>
       <c r="F63">
-        <v>55.632</v>
+        <v>56.544</v>
       </c>
       <c r="G63">
         <v>8.84</v>
@@ -6453,28 +6453,28 @@
         <v>8.275</v>
       </c>
       <c r="M63">
-        <v>5.00688</v>
+        <v>5.08896</v>
       </c>
       <c r="N63">
-        <v>3.268120000000001</v>
+        <v>3.18604</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>3.268120000000001</v>
+        <v>3.18604</v>
       </c>
       <c r="Q63">
-        <v>4.868120000000001</v>
+        <v>4.78604</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1967941145750869</v>
+        <v>0.2007676439060102</v>
       </c>
       <c r="T63">
-        <v>1.29338292947508</v>
+        <v>1.327419322356003</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.652725849231458</v>
+        <v>1.626068980695466</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1320917046842839</v>
+        <v>0.1325337046842839</v>
       </c>
       <c r="C64">
-        <v>27.6145808442538</v>
+        <v>26.31875297878513</v>
       </c>
       <c r="D64">
-        <v>75.3185808442538</v>
+        <v>74.93475297878513</v>
       </c>
       <c r="E64">
-        <v>26.344</v>
+        <v>27.256</v>
       </c>
       <c r="F64">
-        <v>56.544</v>
+        <v>57.456</v>
       </c>
       <c r="G64">
         <v>8.84</v>
@@ -6535,28 +6535,28 @@
         <v>8.275</v>
       </c>
       <c r="M64">
-        <v>5.08896</v>
+        <v>5.171040000000001</v>
       </c>
       <c r="N64">
-        <v>3.18604</v>
+        <v>3.10396</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>3.18604</v>
+        <v>3.10396</v>
       </c>
       <c r="Q64">
-        <v>4.78604</v>
+        <v>4.70396</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2007676439060102</v>
+        <v>0.2049559586061726</v>
       </c>
       <c r="T64">
-        <v>1.327419322356003</v>
+        <v>1.363295520257516</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.626068980695466</v>
+        <v>1.600258361954268</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1325337046842839</v>
+        <v>0.1329757046842839</v>
       </c>
       <c r="C65">
-        <v>26.31875297878513</v>
+        <v>25.02681729674419</v>
       </c>
       <c r="D65">
-        <v>74.93475297878513</v>
+        <v>74.55481729674419</v>
       </c>
       <c r="E65">
-        <v>27.256</v>
+        <v>28.168</v>
       </c>
       <c r="F65">
-        <v>57.456</v>
+        <v>58.368</v>
       </c>
       <c r="G65">
         <v>8.84</v>
@@ -6617,28 +6617,28 @@
         <v>8.275</v>
       </c>
       <c r="M65">
-        <v>5.171040000000001</v>
+        <v>5.25312</v>
       </c>
       <c r="N65">
-        <v>3.10396</v>
+        <v>3.02188</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>3.10396</v>
+        <v>3.02188</v>
       </c>
       <c r="Q65">
-        <v>4.70396</v>
+        <v>4.621880000000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2049559586061726</v>
+        <v>0.2093769574563441</v>
       </c>
       <c r="T65">
-        <v>1.363295520257516</v>
+        <v>1.40116484026467</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.600258361954268</v>
+        <v>1.575254325048733</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1329757046842839</v>
+        <v>0.1334177046842839</v>
       </c>
       <c r="C66">
-        <v>25.02681729674419</v>
+        <v>23.73871489410875</v>
       </c>
       <c r="D66">
-        <v>74.55481729674419</v>
+        <v>74.17871489410875</v>
       </c>
       <c r="E66">
-        <v>28.168</v>
+        <v>29.08</v>
       </c>
       <c r="F66">
-        <v>58.368</v>
+        <v>59.28</v>
       </c>
       <c r="G66">
         <v>8.84</v>
@@ -6699,28 +6699,28 @@
         <v>8.275</v>
       </c>
       <c r="M66">
-        <v>5.25312</v>
+        <v>5.335199999999999</v>
       </c>
       <c r="N66">
-        <v>3.02188</v>
+        <v>2.939800000000001</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>3.02188</v>
+        <v>2.939800000000001</v>
       </c>
       <c r="Q66">
-        <v>4.621880000000001</v>
+        <v>4.539800000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2093769574563441</v>
+        <v>0.2140505848122397</v>
       </c>
       <c r="T66">
-        <v>1.40116484026467</v>
+        <v>1.441198121415089</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.575254325048733</v>
+        <v>1.551019643124906</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1334177046842839</v>
+        <v>0.1338597046842839</v>
       </c>
       <c r="C67">
-        <v>23.73871489410875</v>
+        <v>22.45438804948957</v>
       </c>
       <c r="D67">
-        <v>74.17871489410875</v>
+        <v>73.80638804948957</v>
       </c>
       <c r="E67">
-        <v>29.08</v>
+        <v>29.99200000000001</v>
       </c>
       <c r="F67">
-        <v>59.28</v>
+        <v>60.19200000000001</v>
       </c>
       <c r="G67">
         <v>8.84</v>
@@ -6781,28 +6781,28 @@
         <v>8.275</v>
       </c>
       <c r="M67">
-        <v>5.335199999999999</v>
+        <v>5.417280000000001</v>
       </c>
       <c r="N67">
-        <v>2.939800000000001</v>
+        <v>2.85772</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>2.939800000000001</v>
+        <v>2.85772</v>
       </c>
       <c r="Q67">
-        <v>4.539800000000001</v>
+        <v>4.45772</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2140505848122397</v>
+        <v>0.2189991314243644</v>
       </c>
       <c r="T67">
-        <v>1.441198121415089</v>
+        <v>1.483586301456709</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.551019643124906</v>
+        <v>1.527519345501801</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1338597046842839</v>
+        <v>0.1343017046842839</v>
       </c>
       <c r="C68">
-        <v>22.45438804948957</v>
+        <v>21.17378019459853</v>
       </c>
       <c r="D68">
-        <v>73.80638804948957</v>
+        <v>73.43778019459853</v>
       </c>
       <c r="E68">
-        <v>29.99200000000001</v>
+        <v>30.90400000000001</v>
       </c>
       <c r="F68">
-        <v>60.19200000000001</v>
+        <v>61.10400000000001</v>
       </c>
       <c r="G68">
         <v>8.84</v>
@@ -6863,28 +6863,28 @@
         <v>8.275</v>
       </c>
       <c r="M68">
-        <v>5.417280000000001</v>
+        <v>5.49936</v>
       </c>
       <c r="N68">
-        <v>2.85772</v>
+        <v>2.77564</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2.85772</v>
+        <v>2.77564</v>
       </c>
       <c r="Q68">
-        <v>4.45772</v>
+        <v>4.375640000000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2189991314243644</v>
+        <v>0.2242475899523754</v>
       </c>
       <c r="T68">
-        <v>1.483586301456709</v>
+        <v>1.528543462106912</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.527519345501801</v>
+        <v>1.504720549300282</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1343017046842839</v>
+        <v>0.1733677046842839</v>
       </c>
       <c r="C69">
-        <v>21.17378019459853</v>
+        <v>-2.227613403745593</v>
       </c>
       <c r="D69">
-        <v>73.43778019459853</v>
+        <v>50.94838659625442</v>
       </c>
       <c r="E69">
-        <v>30.90400000000001</v>
+        <v>31.81600000000001</v>
       </c>
       <c r="F69">
-        <v>61.10400000000001</v>
+        <v>62.01600000000001</v>
       </c>
       <c r="G69">
         <v>8.84</v>
@@ -6945,45 +6945,45 @@
         <v>8.275</v>
       </c>
       <c r="M69">
-        <v>5.49936</v>
+        <v>9.103948800000001</v>
       </c>
       <c r="N69">
-        <v>2.77564</v>
+        <v>-0.8289488000000009</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P69">
-        <v>2.77564</v>
+        <v>-0.8289488000000009</v>
       </c>
       <c r="Q69">
-        <v>4.375640000000001</v>
+        <v>0.7710511999999992</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2242475899523754</v>
+        <v>0.2298240771383872</v>
       </c>
       <c r="T69">
-        <v>1.528543462106912</v>
+        <v>1.576310445297754</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.504720549300282</v>
+        <v>0.908946236604494</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1733677046842839</v>
+        <v>0.1743777046842839</v>
       </c>
       <c r="C70">
-        <v>-2.227613403745593</v>
+        <v>-3.539821749263744</v>
       </c>
       <c r="D70">
-        <v>50.94838659625442</v>
+        <v>50.54817825073626</v>
       </c>
       <c r="E70">
-        <v>31.81600000000001</v>
+        <v>32.72800000000001</v>
       </c>
       <c r="F70">
-        <v>62.01600000000001</v>
+        <v>62.928</v>
       </c>
       <c r="G70">
         <v>8.84</v>
@@ -7027,28 +7027,28 @@
         <v>8.275</v>
       </c>
       <c r="M70">
-        <v>9.103948800000001</v>
+        <v>9.237830400000002</v>
       </c>
       <c r="N70">
-        <v>-0.8289488000000009</v>
+        <v>-0.9628304000000014</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-0.8289488000000009</v>
+        <v>-0.9628304000000014</v>
       </c>
       <c r="Q70">
-        <v>0.7710511999999992</v>
+        <v>0.6371695999999987</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2298240771383872</v>
+        <v>0.2357603376912384</v>
       </c>
       <c r="T70">
-        <v>1.576310445297754</v>
+        <v>1.627159169339617</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.908946236604494</v>
+        <v>0.8957731027406607</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1743777046842839</v>
+        <v>0.1753877046842839</v>
       </c>
       <c r="C71">
-        <v>-3.539821749263744</v>
+        <v>-4.845791687674371</v>
       </c>
       <c r="D71">
-        <v>50.54817825073626</v>
+        <v>50.15420831232564</v>
       </c>
       <c r="E71">
-        <v>32.72800000000001</v>
+        <v>33.64000000000001</v>
       </c>
       <c r="F71">
-        <v>62.928</v>
+        <v>63.84000000000001</v>
       </c>
       <c r="G71">
         <v>8.84</v>
@@ -7109,28 +7109,28 @@
         <v>8.275</v>
       </c>
       <c r="M71">
-        <v>9.237830400000002</v>
+        <v>9.371712000000002</v>
       </c>
       <c r="N71">
-        <v>-0.9628304000000014</v>
+        <v>-1.096712000000002</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-0.9628304000000014</v>
+        <v>-1.096712000000002</v>
       </c>
       <c r="Q71">
-        <v>0.6371695999999987</v>
+        <v>0.5032879999999982</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2357603376912384</v>
+        <v>0.242092348947613</v>
       </c>
       <c r="T71">
-        <v>1.627159169339617</v>
+        <v>1.681397808317604</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8957731027406607</v>
+        <v>0.8829763441300797</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1753877046842839</v>
+        <v>0.1763977046842839</v>
       </c>
       <c r="C72">
-        <v>-4.845791687674371</v>
+        <v>-6.145667956387584</v>
       </c>
       <c r="D72">
-        <v>50.15420831232564</v>
+        <v>49.76633204361242</v>
       </c>
       <c r="E72">
-        <v>33.64000000000001</v>
+        <v>34.55200000000001</v>
       </c>
       <c r="F72">
-        <v>63.84000000000001</v>
+        <v>64.75200000000001</v>
       </c>
       <c r="G72">
         <v>8.84</v>
@@ -7191,28 +7191,28 @@
         <v>8.275</v>
       </c>
       <c r="M72">
-        <v>9.371712000000002</v>
+        <v>9.505593600000003</v>
       </c>
       <c r="N72">
-        <v>-1.096712000000002</v>
+        <v>-1.230593600000002</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-1.096712000000002</v>
+        <v>-1.230593600000002</v>
       </c>
       <c r="Q72">
-        <v>0.5032879999999982</v>
+        <v>0.3694063999999977</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.242092348947613</v>
+        <v>0.2488610506354617</v>
       </c>
       <c r="T72">
-        <v>1.681397808317604</v>
+        <v>1.739377043087177</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8829763441300797</v>
+        <v>0.8705400575930364</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1763977046842839</v>
+        <v>0.1774077046842839</v>
       </c>
       <c r="C73">
-        <v>-6.14566795638757</v>
+        <v>-7.439590849767015</v>
       </c>
       <c r="D73">
-        <v>49.76633204361242</v>
+        <v>49.38440915023298</v>
       </c>
       <c r="E73">
-        <v>34.55199999999999</v>
+        <v>35.464</v>
       </c>
       <c r="F73">
-        <v>64.752</v>
+        <v>65.664</v>
       </c>
       <c r="G73">
         <v>8.84</v>
@@ -7273,28 +7273,28 @@
         <v>8.275</v>
       </c>
       <c r="M73">
-        <v>9.505593600000001</v>
+        <v>9.639475200000001</v>
       </c>
       <c r="N73">
-        <v>-1.230593600000001</v>
+        <v>-1.364475200000001</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-1.230593600000001</v>
+        <v>-1.364475200000001</v>
       </c>
       <c r="Q73">
-        <v>0.3694063999999995</v>
+        <v>0.235524799999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2488610506354616</v>
+        <v>0.2561132310152995</v>
       </c>
       <c r="T73">
-        <v>1.739377043087176</v>
+        <v>1.801497651768861</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8705400575930365</v>
+        <v>0.8584492234597999</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1774077046842839</v>
+        <v>0.1784177046842839</v>
       </c>
       <c r="C74">
-        <v>-7.439590849767015</v>
+        <v>-8.727696388318421</v>
       </c>
       <c r="D74">
-        <v>49.38440915023298</v>
+        <v>49.00830361168158</v>
       </c>
       <c r="E74">
-        <v>35.464</v>
+        <v>36.37599999999999</v>
       </c>
       <c r="F74">
-        <v>65.664</v>
+        <v>66.57599999999999</v>
       </c>
       <c r="G74">
         <v>8.84</v>
@@ -7355,28 +7355,28 @@
         <v>8.275</v>
       </c>
       <c r="M74">
-        <v>9.639475200000001</v>
+        <v>9.7733568</v>
       </c>
       <c r="N74">
-        <v>-1.364475200000001</v>
+        <v>-1.4983568</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-1.364475200000001</v>
+        <v>-1.4983568</v>
       </c>
       <c r="Q74">
-        <v>0.235524799999999</v>
+        <v>0.1016432000000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2561132310152995</v>
+        <v>0.2639026099417921</v>
       </c>
       <c r="T74">
-        <v>1.801497651768861</v>
+        <v>1.868219787019559</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8584492234597999</v>
+        <v>0.8466896450562411</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1784177046842839</v>
+        <v>0.1794277046842839</v>
       </c>
       <c r="C75">
-        <v>-8.727696388318421</v>
+        <v>-10.0101164802054</v>
       </c>
       <c r="D75">
-        <v>49.00830361168158</v>
+        <v>48.6378835197946</v>
       </c>
       <c r="E75">
-        <v>36.37599999999999</v>
+        <v>37.288</v>
       </c>
       <c r="F75">
-        <v>66.57599999999999</v>
+        <v>67.488</v>
       </c>
       <c r="G75">
         <v>8.84</v>
@@ -7437,28 +7437,28 @@
         <v>8.275</v>
       </c>
       <c r="M75">
-        <v>9.7733568</v>
+        <v>9.907238400000001</v>
       </c>
       <c r="N75">
-        <v>-1.4983568</v>
+        <v>-1.6322384</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-1.4983568</v>
+        <v>-1.6322384</v>
       </c>
       <c r="Q75">
-        <v>0.1016432000000003</v>
+        <v>-0.03223840000000022</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2639026099417921</v>
+        <v>0.2722911718626302</v>
       </c>
       <c r="T75">
-        <v>1.868219787019559</v>
+        <v>1.940074394212619</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8466896450562411</v>
+        <v>0.8352478930960215</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1794277046842839</v>
+        <v>0.1804377046842839</v>
       </c>
       <c r="C76">
-        <v>-10.0101164802054</v>
+        <v>-11.28697907549538</v>
       </c>
       <c r="D76">
-        <v>48.6378835197946</v>
+        <v>48.27302092450463</v>
       </c>
       <c r="E76">
-        <v>37.288</v>
+        <v>38.2</v>
       </c>
       <c r="F76">
-        <v>67.488</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G76">
         <v>8.84</v>
@@ -7519,28 +7519,28 @@
         <v>8.275</v>
       </c>
       <c r="M76">
-        <v>9.907238400000001</v>
+        <v>10.04112</v>
       </c>
       <c r="N76">
-        <v>-1.6322384</v>
+        <v>-1.766120000000001</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-1.6322384</v>
+        <v>-1.766120000000001</v>
       </c>
       <c r="Q76">
-        <v>-0.03223840000000022</v>
+        <v>-0.1661200000000007</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2722911718626302</v>
+        <v>0.2813508187371355</v>
       </c>
       <c r="T76">
-        <v>1.940074394212619</v>
+        <v>2.017677369981124</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8352478930960215</v>
+        <v>0.8241112545214079</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1804377046842839</v>
+        <v>0.1814477046842839</v>
       </c>
       <c r="C77">
-        <v>-11.28697907549538</v>
+        <v>-12.55840831351476</v>
       </c>
       <c r="D77">
-        <v>48.27302092450463</v>
+        <v>47.91359168648524</v>
       </c>
       <c r="E77">
-        <v>38.2</v>
+        <v>39.11199999999999</v>
       </c>
       <c r="F77">
-        <v>68.40000000000001</v>
+        <v>69.312</v>
       </c>
       <c r="G77">
         <v>8.84</v>
@@ -7601,28 +7601,28 @@
         <v>8.275</v>
       </c>
       <c r="M77">
-        <v>10.04112</v>
+        <v>10.1750016</v>
       </c>
       <c r="N77">
-        <v>-1.766120000000001</v>
+        <v>-1.9000016</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-1.766120000000001</v>
+        <v>-1.9000016</v>
       </c>
       <c r="Q77">
-        <v>-0.1661200000000007</v>
+        <v>-0.3000015999999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2813508187371355</v>
+        <v>0.2911654361845162</v>
       </c>
       <c r="T77">
-        <v>2.017677369981124</v>
+        <v>2.101747260397005</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8241112545214079</v>
+        <v>0.8132676853829685</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1814477046842839</v>
+        <v>0.1824577046842839</v>
       </c>
       <c r="C78">
-        <v>-12.55840831351476</v>
+        <v>-13.82452466366969</v>
       </c>
       <c r="D78">
-        <v>47.91359168648524</v>
+        <v>47.55947533633031</v>
       </c>
       <c r="E78">
-        <v>39.11199999999999</v>
+        <v>40.024</v>
       </c>
       <c r="F78">
-        <v>69.312</v>
+        <v>70.224</v>
       </c>
       <c r="G78">
         <v>8.84</v>
@@ -7683,28 +7683,28 @@
         <v>8.275</v>
       </c>
       <c r="M78">
-        <v>10.1750016</v>
+        <v>10.3088832</v>
       </c>
       <c r="N78">
-        <v>-1.9000016</v>
+        <v>-2.033883200000002</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-1.9000016</v>
+        <v>-2.033883200000002</v>
       </c>
       <c r="Q78">
-        <v>-0.3000015999999994</v>
+        <v>-0.4338832000000017</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2911654361845162</v>
+        <v>0.3018334986273212</v>
       </c>
       <c r="T78">
-        <v>2.101747260397005</v>
+        <v>2.193127576066439</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8132676853829685</v>
+        <v>0.8027057673909817</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1824577046842839</v>
+        <v>0.2255877046842839</v>
       </c>
       <c r="C79">
-        <v>-13.82452466366969</v>
+        <v>-26.14575965478328</v>
       </c>
       <c r="D79">
-        <v>47.55947533633031</v>
+        <v>36.15024034521673</v>
       </c>
       <c r="E79">
-        <v>40.024</v>
+        <v>40.93600000000001</v>
       </c>
       <c r="F79">
-        <v>70.224</v>
+        <v>71.13600000000001</v>
       </c>
       <c r="G79">
         <v>8.84</v>
@@ -7765,45 +7765,45 @@
         <v>8.275</v>
       </c>
       <c r="M79">
-        <v>10.3088832</v>
+        <v>14.2841088</v>
       </c>
       <c r="N79">
-        <v>-2.033883200000002</v>
+        <v>-6.009108800000002</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-2.033883200000002</v>
+        <v>-6.009108800000002</v>
       </c>
       <c r="Q79">
-        <v>-0.4338832000000017</v>
+        <v>-4.409108800000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3018334986273212</v>
+        <v>0.3134713849285631</v>
       </c>
       <c r="T79">
-        <v>2.193127576066439</v>
+        <v>2.292815193160369</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8027057673909817</v>
+        <v>0.5793151057488444</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2255877046842839</v>
+        <v>0.2271377046842839</v>
       </c>
       <c r="C80">
-        <v>-26.14575965478328</v>
+        <v>-27.36675701764635</v>
       </c>
       <c r="D80">
-        <v>36.15024034521673</v>
+        <v>35.84124298235366</v>
       </c>
       <c r="E80">
-        <v>40.93600000000001</v>
+        <v>41.848</v>
       </c>
       <c r="F80">
-        <v>71.13600000000001</v>
+        <v>72.048</v>
       </c>
       <c r="G80">
         <v>8.84</v>
@@ -7847,28 +7847,28 @@
         <v>8.275</v>
       </c>
       <c r="M80">
-        <v>14.2841088</v>
+        <v>14.4672384</v>
       </c>
       <c r="N80">
-        <v>-6.009108800000002</v>
+        <v>-6.192238400000001</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-6.009108800000002</v>
+        <v>-6.192238400000001</v>
       </c>
       <c r="Q80">
-        <v>-4.409108800000002</v>
+        <v>-4.592238400000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3134713849285631</v>
+        <v>0.3262176413537328</v>
       </c>
       <c r="T80">
-        <v>2.292815193160369</v>
+        <v>2.401996869025148</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5793151057488444</v>
+        <v>0.5719820031444287</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2271377046842839</v>
+        <v>0.2286877046842839</v>
       </c>
       <c r="C81">
-        <v>-27.36675701764635</v>
+        <v>-28.58251678497761</v>
       </c>
       <c r="D81">
-        <v>35.84124298235366</v>
+        <v>35.5374832150224</v>
       </c>
       <c r="E81">
-        <v>41.848</v>
+        <v>42.76000000000001</v>
       </c>
       <c r="F81">
-        <v>72.048</v>
+        <v>72.96000000000001</v>
       </c>
       <c r="G81">
         <v>8.84</v>
@@ -7929,28 +7929,28 @@
         <v>8.275</v>
       </c>
       <c r="M81">
-        <v>14.4672384</v>
+        <v>14.650368</v>
       </c>
       <c r="N81">
-        <v>-6.192238400000001</v>
+        <v>-6.375368000000002</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-6.192238400000001</v>
+        <v>-6.375368000000002</v>
       </c>
       <c r="Q81">
-        <v>-4.592238400000001</v>
+        <v>-4.775368000000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3262176413537328</v>
+        <v>0.3402385234214194</v>
       </c>
       <c r="T81">
-        <v>2.401996869025148</v>
+        <v>2.522096712476406</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5719820031444287</v>
+        <v>0.5648322281051232</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2286877046842839</v>
+        <v>0.2302377046842839</v>
       </c>
       <c r="C82">
-        <v>-28.58251678497761</v>
+        <v>-29.79317100580289</v>
       </c>
       <c r="D82">
-        <v>35.5374832150224</v>
+        <v>35.23882899419713</v>
       </c>
       <c r="E82">
-        <v>42.76000000000001</v>
+        <v>43.67200000000001</v>
       </c>
       <c r="F82">
-        <v>72.96000000000001</v>
+        <v>73.87200000000001</v>
       </c>
       <c r="G82">
         <v>8.84</v>
@@ -8011,28 +8011,28 @@
         <v>8.275</v>
       </c>
       <c r="M82">
-        <v>14.650368</v>
+        <v>14.8334976</v>
       </c>
       <c r="N82">
-        <v>-6.375368000000002</v>
+        <v>-6.558497600000003</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-6.375368000000002</v>
+        <v>-6.558497600000003</v>
       </c>
       <c r="Q82">
-        <v>-4.775368000000002</v>
+        <v>-4.958497600000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3402385234214194</v>
+        <v>0.3557352878120205</v>
       </c>
       <c r="T82">
-        <v>2.522096712476406</v>
+        <v>2.654838644712006</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5648322281051232</v>
+        <v>0.5578589907211093</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2302377046842839</v>
+        <v>0.2317877046842839</v>
       </c>
       <c r="C83">
-        <v>-29.79317100580289</v>
+        <v>-30.99884732722275</v>
       </c>
       <c r="D83">
-        <v>35.23882899419713</v>
+        <v>34.94515267277725</v>
       </c>
       <c r="E83">
-        <v>43.67200000000001</v>
+        <v>44.584</v>
       </c>
       <c r="F83">
-        <v>73.87200000000001</v>
+        <v>74.78400000000001</v>
       </c>
       <c r="G83">
         <v>8.84</v>
@@ -8093,28 +8093,28 @@
         <v>8.275</v>
       </c>
       <c r="M83">
-        <v>14.8334976</v>
+        <v>15.0166272</v>
       </c>
       <c r="N83">
-        <v>-6.558497600000003</v>
+        <v>-6.741627200000002</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-6.558497600000003</v>
+        <v>-6.741627200000002</v>
       </c>
       <c r="Q83">
-        <v>-4.958497600000003</v>
+        <v>-5.141627200000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3557352878120205</v>
+        <v>0.3729539149126883</v>
       </c>
       <c r="T83">
-        <v>2.654838644712006</v>
+        <v>2.80232968052934</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5578589907211093</v>
+        <v>0.5510558322976813</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2317877046842839</v>
+        <v>0.2333377046842839</v>
       </c>
       <c r="C84">
-        <v>-30.99884732722275</v>
+        <v>-32.19966917632233</v>
       </c>
       <c r="D84">
-        <v>34.94515267277725</v>
+        <v>34.65633082367768</v>
       </c>
       <c r="E84">
-        <v>44.584</v>
+        <v>45.49600000000001</v>
       </c>
       <c r="F84">
-        <v>74.78400000000001</v>
+        <v>75.69600000000001</v>
       </c>
       <c r="G84">
         <v>8.84</v>
@@ -8175,28 +8175,28 @@
         <v>8.275</v>
       </c>
       <c r="M84">
-        <v>15.0166272</v>
+        <v>15.1997568</v>
       </c>
       <c r="N84">
-        <v>-6.741627200000002</v>
+        <v>-6.924756800000003</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-6.741627200000002</v>
+        <v>-6.924756800000003</v>
       </c>
       <c r="Q84">
-        <v>-5.141627200000002</v>
+        <v>-5.324756800000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3729539149126883</v>
+        <v>0.3921982628487288</v>
       </c>
       <c r="T84">
-        <v>2.80232968052934</v>
+        <v>2.967172602913419</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5510558322976813</v>
+        <v>0.5444166054025285</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2333377046842839</v>
+        <v>0.2348877046842839</v>
       </c>
       <c r="C85">
-        <v>-32.19966917632233</v>
+        <v>-33.39575593313388</v>
       </c>
       <c r="D85">
-        <v>34.65633082367768</v>
+        <v>34.37224406686612</v>
       </c>
       <c r="E85">
-        <v>45.49600000000001</v>
+        <v>46.408</v>
       </c>
       <c r="F85">
-        <v>75.69600000000001</v>
+        <v>76.608</v>
       </c>
       <c r="G85">
         <v>8.84</v>
@@ -8257,28 +8257,28 @@
         <v>8.275</v>
       </c>
       <c r="M85">
-        <v>15.1997568</v>
+        <v>15.3828864</v>
       </c>
       <c r="N85">
-        <v>-6.924756800000003</v>
+        <v>-7.107886400000002</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-6.924756800000003</v>
+        <v>-7.107886400000002</v>
       </c>
       <c r="Q85">
-        <v>-5.324756800000003</v>
+        <v>-5.507886400000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3921982628487288</v>
+        <v>0.4138481542767745</v>
       </c>
       <c r="T85">
-        <v>2.967172602913419</v>
+        <v>3.152620890595509</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5444166054025285</v>
+        <v>0.5379354553382127</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2348877046842839</v>
+        <v>0.2364377046842839</v>
       </c>
       <c r="C86">
-        <v>-33.39575593313388</v>
+        <v>-34.58722309516183</v>
       </c>
       <c r="D86">
-        <v>34.37224406686612</v>
+        <v>34.09277690483816</v>
       </c>
       <c r="E86">
-        <v>46.408</v>
+        <v>47.31999999999999</v>
       </c>
       <c r="F86">
-        <v>76.608</v>
+        <v>77.52</v>
       </c>
       <c r="G86">
         <v>8.84</v>
@@ -8339,28 +8339,28 @@
         <v>8.275</v>
       </c>
       <c r="M86">
-        <v>15.3828864</v>
+        <v>15.566016</v>
       </c>
       <c r="N86">
-        <v>-7.107886400000002</v>
+        <v>-7.291015999999999</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-7.107886400000002</v>
+        <v>-7.291015999999999</v>
       </c>
       <c r="Q86">
-        <v>-5.507886400000002</v>
+        <v>-5.691015999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4138481542767742</v>
+        <v>0.4383846978952258</v>
       </c>
       <c r="T86">
-        <v>3.152620890595506</v>
+        <v>3.362795616635207</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5379354553382127</v>
+        <v>0.5316068029224691</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2364377046842839</v>
+        <v>0.2379877046842839</v>
       </c>
       <c r="C87">
-        <v>-34.58722309516183</v>
+        <v>-35.77418243394634</v>
       </c>
       <c r="D87">
-        <v>34.09277690483816</v>
+        <v>33.81781756605366</v>
       </c>
       <c r="E87">
-        <v>47.31999999999999</v>
+        <v>48.232</v>
       </c>
       <c r="F87">
-        <v>77.52</v>
+        <v>78.432</v>
       </c>
       <c r="G87">
         <v>8.84</v>
@@ -8421,28 +8421,28 @@
         <v>8.275</v>
       </c>
       <c r="M87">
-        <v>15.566016</v>
+        <v>15.7491456</v>
       </c>
       <c r="N87">
-        <v>-7.291015999999999</v>
+        <v>-7.4741456</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-7.291015999999999</v>
+        <v>-7.4741456</v>
       </c>
       <c r="Q87">
-        <v>-5.691015999999999</v>
+        <v>-5.8741456</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4383846978952258</v>
+        <v>0.4664264620305991</v>
       </c>
       <c r="T87">
-        <v>3.362795616635207</v>
+        <v>3.602995303537722</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5316068029224691</v>
+        <v>0.5254253284698822</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2379877046842839</v>
+        <v>0.2395377046842839</v>
       </c>
       <c r="C88">
-        <v>-35.77418243394634</v>
+        <v>-36.95674214411119</v>
       </c>
       <c r="D88">
-        <v>33.81781756605366</v>
+        <v>33.54725785588882</v>
       </c>
       <c r="E88">
-        <v>48.232</v>
+        <v>49.14400000000001</v>
       </c>
       <c r="F88">
-        <v>78.432</v>
+        <v>79.34400000000001</v>
       </c>
       <c r="G88">
         <v>8.84</v>
@@ -8503,28 +8503,28 @@
         <v>8.275</v>
       </c>
       <c r="M88">
-        <v>15.7491456</v>
+        <v>15.9322752</v>
       </c>
       <c r="N88">
-        <v>-7.4741456</v>
+        <v>-7.657275200000003</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-7.4741456</v>
+        <v>-7.657275200000003</v>
       </c>
       <c r="Q88">
-        <v>-5.8741456</v>
+        <v>-6.057275200000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4664264620305991</v>
+        <v>0.4987823437252605</v>
       </c>
       <c r="T88">
-        <v>3.602995303537722</v>
+        <v>3.880148788425239</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5254253284698822</v>
+        <v>0.5193859568782743</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2395377046842839</v>
+        <v>0.2410877046842839</v>
       </c>
       <c r="C89">
-        <v>-36.95674214411119</v>
+        <v>-38.13500698531402</v>
       </c>
       <c r="D89">
-        <v>33.54725785588882</v>
+        <v>33.28099301468598</v>
       </c>
       <c r="E89">
-        <v>49.14400000000001</v>
+        <v>50.056</v>
       </c>
       <c r="F89">
-        <v>79.34400000000001</v>
+        <v>80.256</v>
       </c>
       <c r="G89">
         <v>8.84</v>
@@ -8585,28 +8585,28 @@
         <v>8.275</v>
       </c>
       <c r="M89">
-        <v>15.9322752</v>
+        <v>16.1154048</v>
       </c>
       <c r="N89">
-        <v>-7.657275200000003</v>
+        <v>-7.8404048</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-7.657275200000003</v>
+        <v>-7.8404048</v>
       </c>
       <c r="Q89">
-        <v>-6.057275200000003</v>
+        <v>-6.2404048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4987823437252605</v>
+        <v>0.5365308723690323</v>
       </c>
       <c r="T89">
-        <v>3.880148788425239</v>
+        <v>4.20349452079401</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5193859568782743</v>
+        <v>0.5134838437319303</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2410877046842839</v>
+        <v>0.2426377046842839</v>
       </c>
       <c r="C90">
-        <v>-38.13500698531402</v>
+        <v>-39.3090784174896</v>
       </c>
       <c r="D90">
-        <v>33.28099301468598</v>
+        <v>33.0189215825104</v>
       </c>
       <c r="E90">
-        <v>50.056</v>
+        <v>50.968</v>
       </c>
       <c r="F90">
-        <v>80.256</v>
+        <v>81.16800000000001</v>
       </c>
       <c r="G90">
         <v>8.84</v>
@@ -8667,28 +8667,28 @@
         <v>8.275</v>
       </c>
       <c r="M90">
-        <v>16.1154048</v>
+        <v>16.2985344</v>
       </c>
       <c r="N90">
-        <v>-7.8404048</v>
+        <v>-8.023534400000001</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-7.8404048</v>
+        <v>-8.023534400000001</v>
       </c>
       <c r="Q90">
-        <v>-6.2404048</v>
+        <v>-6.423534400000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5365308723690323</v>
+        <v>0.5811427698571261</v>
       </c>
       <c r="T90">
-        <v>4.20349452079401</v>
+        <v>4.585630386320737</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5134838437319303</v>
+        <v>0.507714362341684</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2426377046842839</v>
+        <v>0.2441877046842839</v>
       </c>
       <c r="C91">
-        <v>-39.3090784174896</v>
+        <v>-40.47905472975319</v>
       </c>
       <c r="D91">
-        <v>33.0189215825104</v>
+        <v>32.76094527024681</v>
       </c>
       <c r="E91">
-        <v>50.968</v>
+        <v>51.88</v>
       </c>
       <c r="F91">
-        <v>81.16800000000001</v>
+        <v>82.08</v>
       </c>
       <c r="G91">
         <v>8.84</v>
@@ -8749,28 +8749,28 @@
         <v>8.275</v>
       </c>
       <c r="M91">
-        <v>16.2985344</v>
+        <v>16.481664</v>
       </c>
       <c r="N91">
-        <v>-8.023534400000001</v>
+        <v>-8.206663999999998</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-8.023534400000001</v>
+        <v>-8.206663999999998</v>
       </c>
       <c r="Q91">
-        <v>-6.423534400000001</v>
+        <v>-6.606663999999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5811427698571261</v>
+        <v>0.6346770468428388</v>
       </c>
       <c r="T91">
-        <v>4.585630386320737</v>
+        <v>5.044193424952812</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.507714362341684</v>
+        <v>0.5020730916489986</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2441877046842839</v>
+        <v>0.2775877046842839</v>
       </c>
       <c r="C92">
-        <v>-40.47905472975319</v>
+        <v>-46.11182097366016</v>
       </c>
       <c r="D92">
-        <v>32.76094527024681</v>
+        <v>28.04017902633985</v>
       </c>
       <c r="E92">
-        <v>51.88</v>
+        <v>52.792</v>
       </c>
       <c r="F92">
-        <v>82.08</v>
+        <v>82.992</v>
       </c>
       <c r="G92">
         <v>8.84</v>
@@ -8831,45 +8831,45 @@
         <v>8.275</v>
       </c>
       <c r="M92">
-        <v>16.481664</v>
+        <v>19.5695136</v>
       </c>
       <c r="N92">
-        <v>-8.206663999999998</v>
+        <v>-11.2945136</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-8.206663999999998</v>
+        <v>-11.2945136</v>
       </c>
       <c r="Q92">
-        <v>-6.606663999999999</v>
+        <v>-9.694513600000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6346770468428388</v>
+        <v>0.7001078298253766</v>
       </c>
       <c r="T92">
-        <v>5.044193424952812</v>
+        <v>5.604659361058681</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5020730916489986</v>
+        <v>0.4228515930002471</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2775877046842839</v>
+        <v>0.2794877046842839</v>
       </c>
       <c r="C93">
-        <v>-46.11182097366016</v>
+        <v>-47.25180190326031</v>
       </c>
       <c r="D93">
-        <v>28.04017902633985</v>
+        <v>27.8121980967397</v>
       </c>
       <c r="E93">
-        <v>52.792</v>
+        <v>53.70400000000001</v>
       </c>
       <c r="F93">
-        <v>82.992</v>
+        <v>83.90400000000001</v>
       </c>
       <c r="G93">
         <v>8.84</v>
@@ -8913,28 +8913,28 @@
         <v>8.275</v>
       </c>
       <c r="M93">
-        <v>19.5695136</v>
+        <v>19.7845632</v>
       </c>
       <c r="N93">
-        <v>-11.2945136</v>
+        <v>-11.5095632</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-11.2945136</v>
+        <v>-11.5095632</v>
       </c>
       <c r="Q93">
-        <v>-9.694513600000001</v>
+        <v>-9.909563200000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7001078298253766</v>
+        <v>0.7818963085535489</v>
       </c>
       <c r="T93">
-        <v>5.604659361058681</v>
+        <v>6.305241781191017</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4228515930002471</v>
+        <v>0.418255380032853</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2794877046842839</v>
+        <v>0.2813877046842839</v>
       </c>
       <c r="C94">
-        <v>-47.25180190326031</v>
+        <v>-48.38810552918432</v>
       </c>
       <c r="D94">
-        <v>27.8121980967397</v>
+        <v>27.58789447081568</v>
       </c>
       <c r="E94">
-        <v>53.70400000000001</v>
+        <v>54.616</v>
       </c>
       <c r="F94">
-        <v>83.90400000000001</v>
+        <v>84.816</v>
       </c>
       <c r="G94">
         <v>8.84</v>
@@ -8995,28 +8995,28 @@
         <v>8.275</v>
       </c>
       <c r="M94">
-        <v>19.7845632</v>
+        <v>19.9996128</v>
       </c>
       <c r="N94">
-        <v>-11.5095632</v>
+        <v>-11.7246128</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-11.5095632</v>
+        <v>-11.7246128</v>
       </c>
       <c r="Q94">
-        <v>-9.909563200000004</v>
+        <v>-10.1246128</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7818963085535489</v>
+        <v>0.8870529240611987</v>
       </c>
       <c r="T94">
-        <v>6.305241781191017</v>
+        <v>7.205990607075449</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.418255380032853</v>
+        <v>0.4137580103550804</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2813877046842839</v>
+        <v>0.2832877046842839</v>
       </c>
       <c r="C95">
-        <v>-48.38810552918432</v>
+        <v>-49.52082011128968</v>
       </c>
       <c r="D95">
-        <v>27.58789447081568</v>
+        <v>27.36717988871033</v>
       </c>
       <c r="E95">
-        <v>54.616</v>
+        <v>55.52800000000001</v>
       </c>
       <c r="F95">
-        <v>84.816</v>
+        <v>85.72800000000001</v>
       </c>
       <c r="G95">
         <v>8.84</v>
@@ -9077,28 +9077,28 @@
         <v>8.275</v>
       </c>
       <c r="M95">
-        <v>19.9996128</v>
+        <v>20.2146624</v>
       </c>
       <c r="N95">
-        <v>-11.7246128</v>
+        <v>-11.9396624</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-11.7246128</v>
+        <v>-11.9396624</v>
       </c>
       <c r="Q95">
-        <v>-10.1246128</v>
+        <v>-10.3396624</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8870529240611987</v>
+        <v>1.027261744738066</v>
       </c>
       <c r="T95">
-        <v>7.205990607075449</v>
+        <v>8.406989041588027</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4137580103550804</v>
+        <v>0.4093563293938562</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2832877046842839</v>
+        <v>0.2851877046842839</v>
       </c>
       <c r="C96">
-        <v>-49.52082011128968</v>
+        <v>-50.65003110738962</v>
       </c>
       <c r="D96">
-        <v>27.36717988871033</v>
+        <v>27.14996889261039</v>
       </c>
       <c r="E96">
-        <v>55.52800000000001</v>
+        <v>56.44000000000001</v>
       </c>
       <c r="F96">
-        <v>85.72800000000001</v>
+        <v>86.64000000000001</v>
       </c>
       <c r="G96">
         <v>8.84</v>
@@ -9159,28 +9159,28 @@
         <v>8.275</v>
       </c>
       <c r="M96">
-        <v>20.2146624</v>
+        <v>20.42971200000001</v>
       </c>
       <c r="N96">
-        <v>-11.9396624</v>
+        <v>-12.15471200000001</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-11.9396624</v>
+        <v>-12.15471200000001</v>
       </c>
       <c r="Q96">
-        <v>-10.3396624</v>
+        <v>-10.55471200000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.027261744738066</v>
+        <v>1.223554093685679</v>
       </c>
       <c r="T96">
-        <v>8.406989041588027</v>
+        <v>10.08838684990564</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4093563293938562</v>
+        <v>0.4050473154002365</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2851877046842839</v>
+        <v>0.2870877046842839</v>
       </c>
       <c r="C97">
-        <v>-50.65003110738962</v>
+        <v>-51.77582128357557</v>
       </c>
       <c r="D97">
-        <v>27.14996889261039</v>
+        <v>26.93617871642443</v>
       </c>
       <c r="E97">
-        <v>56.44000000000001</v>
+        <v>57.352</v>
       </c>
       <c r="F97">
-        <v>86.64000000000001</v>
+        <v>87.55200000000001</v>
       </c>
       <c r="G97">
         <v>8.84</v>
@@ -9241,28 +9241,28 @@
         <v>8.275</v>
       </c>
       <c r="M97">
-        <v>20.42971200000001</v>
+        <v>20.6447616</v>
       </c>
       <c r="N97">
-        <v>-12.15471200000001</v>
+        <v>-12.3697616</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-12.15471200000001</v>
+        <v>-12.3697616</v>
       </c>
       <c r="Q97">
-        <v>-10.55471200000001</v>
+        <v>-10.7697616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.223554093685679</v>
+        <v>1.5179926171071</v>
       </c>
       <c r="T97">
-        <v>10.08838684990564</v>
+        <v>12.61048356238205</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4050473154002365</v>
+        <v>0.4008280725314842</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2870877046842839</v>
+        <v>0.2889877046842839</v>
       </c>
       <c r="C98">
-        <v>-51.77582128357556</v>
+        <v>-52.89827081936788</v>
       </c>
       <c r="D98">
-        <v>26.93617871642443</v>
+        <v>26.72572918063211</v>
       </c>
       <c r="E98">
-        <v>57.35199999999999</v>
+        <v>58.264</v>
       </c>
       <c r="F98">
-        <v>87.55199999999999</v>
+        <v>88.464</v>
       </c>
       <c r="G98">
         <v>8.84</v>
@@ -9323,28 +9323,28 @@
         <v>8.275</v>
       </c>
       <c r="M98">
-        <v>20.6447616</v>
+        <v>20.8598112</v>
       </c>
       <c r="N98">
-        <v>-12.3697616</v>
+        <v>-12.5848112</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-12.3697616</v>
+        <v>-12.5848112</v>
       </c>
       <c r="Q98">
-        <v>-10.7697616</v>
+        <v>-10.9848112</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.517992617107096</v>
+        <v>2.008723489476128</v>
       </c>
       <c r="T98">
-        <v>12.61048356238202</v>
+        <v>16.81397808317602</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4008280725314842</v>
+        <v>0.3966958243610565</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2889877046842839</v>
+        <v>0.2908877046842839</v>
       </c>
       <c r="C99">
-        <v>-52.89827081936788</v>
+        <v>-54.01745740797548</v>
       </c>
       <c r="D99">
-        <v>26.72572918063211</v>
+        <v>26.51854259202453</v>
       </c>
       <c r="E99">
-        <v>58.264</v>
+        <v>59.176</v>
       </c>
       <c r="F99">
-        <v>88.464</v>
+        <v>89.376</v>
       </c>
       <c r="G99">
         <v>8.84</v>
@@ -9405,28 +9405,28 @@
         <v>8.275</v>
       </c>
       <c r="M99">
-        <v>20.8598112</v>
+        <v>21.0748608</v>
       </c>
       <c r="N99">
-        <v>-12.5848112</v>
+        <v>-12.7998608</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-12.5848112</v>
+        <v>-12.7998608</v>
       </c>
       <c r="Q99">
-        <v>-10.9848112</v>
+        <v>-11.1998608</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.008723489476128</v>
+        <v>2.990185234214191</v>
       </c>
       <c r="T99">
-        <v>16.81397808317602</v>
+        <v>25.22096712476403</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3966958243610565</v>
+        <v>0.3926479077859437</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2908877046842839</v>
+        <v>0.2927877046842839</v>
       </c>
       <c r="C100">
-        <v>-54.01745740797548</v>
+        <v>-55.13345635192798</v>
       </c>
       <c r="D100">
-        <v>26.51854259202453</v>
+        <v>26.31454364807202</v>
       </c>
       <c r="E100">
-        <v>59.176</v>
+        <v>60.08799999999999</v>
       </c>
       <c r="F100">
-        <v>89.376</v>
+        <v>90.288</v>
       </c>
       <c r="G100">
         <v>8.84</v>
@@ -9487,28 +9487,28 @@
         <v>8.275</v>
       </c>
       <c r="M100">
-        <v>21.0748608</v>
+        <v>21.2899104</v>
       </c>
       <c r="N100">
-        <v>-12.7998608</v>
+        <v>-13.0149104</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-12.7998608</v>
+        <v>-13.0149104</v>
       </c>
       <c r="Q100">
-        <v>-11.1998608</v>
+        <v>-11.4149104</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.990185234214191</v>
+        <v>5.934570468428382</v>
       </c>
       <c r="T100">
-        <v>25.22096712476403</v>
+        <v>50.44193424952807</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3926479077859437</v>
+        <v>0.3886817673032574</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2927877046842839</v>
-      </c>
-      <c r="C101">
-        <v>-55.13345635192798</v>
-      </c>
-      <c r="D101">
-        <v>26.31454364807202</v>
-      </c>
-      <c r="E101">
-        <v>60.08799999999999</v>
-      </c>
-      <c r="F101">
-        <v>90.288</v>
-      </c>
-      <c r="G101">
-        <v>8.84</v>
-      </c>
-      <c r="H101">
-        <v>61</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.875</v>
-      </c>
-      <c r="K101">
-        <v>1.6</v>
-      </c>
-      <c r="L101">
-        <v>8.275</v>
-      </c>
-      <c r="M101">
-        <v>21.2899104</v>
-      </c>
-      <c r="N101">
-        <v>-13.0149104</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-13.0149104</v>
-      </c>
-      <c r="Q101">
-        <v>-11.4149104</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.934570468428382</v>
-      </c>
-      <c r="T101">
-        <v>50.44193424952807</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3886817673032574</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
